--- a/research/traditional_assets/database/data/belgium/belgium_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07844143275977961</v>
+        <v>0.07827907917788014</v>
       </c>
       <c r="C2">
-        <v>3269.82670759425</v>
+        <v>3237.889870961472</v>
       </c>
       <c r="D2">
-        <v>3221.62670759425</v>
+        <v>3223.040870961473</v>
       </c>
       <c r="E2">
-        <v>-2299.4</v>
+        <v>-2266.049</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33.35100000000001</v>
       </c>
       <c r="G2">
         <v>48.2</v>
@@ -1457,28 +1457,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6775553</v>
       </c>
       <c r="N2">
-        <v>467.8333333333333</v>
+        <v>466.1557780333333</v>
       </c>
       <c r="O2">
-        <v>116.9583333333333</v>
+        <v>116.5389445083333</v>
       </c>
       <c r="P2">
-        <v>350.8749999999999</v>
+        <v>349.6168335249999</v>
       </c>
       <c r="Q2">
-        <v>831.875</v>
+        <v>830.6168335249999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07844143275977961</v>
+        <v>0.07868871634129308</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549505</v>
+        <v>0.6410622972273365</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>278.8780395694456</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07827907917788014</v>
+        <v>0.07811672559598071</v>
       </c>
       <c r="C3">
-        <v>3237.889870961472</v>
+        <v>3205.954276394553</v>
       </c>
       <c r="D3">
-        <v>3223.040870961473</v>
+        <v>3224.456276394554</v>
       </c>
       <c r="E3">
-        <v>-2266.049</v>
+        <v>-2232.698</v>
       </c>
       <c r="F3">
-        <v>33.35100000000001</v>
+        <v>66.70200000000001</v>
       </c>
       <c r="G3">
         <v>48.2</v>
@@ -1539,28 +1539,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M3">
-        <v>1.6775553</v>
+        <v>3.355110600000001</v>
       </c>
       <c r="N3">
-        <v>466.1557780333333</v>
+        <v>464.4782227333333</v>
       </c>
       <c r="O3">
-        <v>116.5389445083333</v>
+        <v>116.1195556833333</v>
       </c>
       <c r="P3">
-        <v>349.6168335249999</v>
+        <v>348.35866705</v>
       </c>
       <c r="Q3">
-        <v>830.6168335249999</v>
+        <v>829.3586670499999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07868871634129308</v>
+        <v>0.07894104652651092</v>
       </c>
       <c r="T3">
-        <v>0.6410622972273365</v>
+        <v>0.6459806821991591</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>278.8780395694456</v>
+        <v>139.4390197847228</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07811672559598071</v>
+        <v>0.07795437201408124</v>
       </c>
       <c r="C4">
-        <v>3205.954276394553</v>
+        <v>3174.01992553058</v>
       </c>
       <c r="D4">
-        <v>3224.456276394554</v>
+        <v>3225.87292553058</v>
       </c>
       <c r="E4">
-        <v>-2232.698</v>
+        <v>-2199.347</v>
       </c>
       <c r="F4">
-        <v>66.70200000000001</v>
+        <v>100.053</v>
       </c>
       <c r="G4">
         <v>48.2</v>
@@ -1621,28 +1621,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M4">
-        <v>3.355110600000001</v>
+        <v>5.0326659</v>
       </c>
       <c r="N4">
-        <v>464.4782227333333</v>
+        <v>462.8006674333333</v>
       </c>
       <c r="O4">
-        <v>116.1195556833333</v>
+        <v>115.7001668583333</v>
       </c>
       <c r="P4">
-        <v>348.35866705</v>
+        <v>347.100500575</v>
       </c>
       <c r="Q4">
-        <v>829.3586670499999</v>
+        <v>828.100500575</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07894104652651092</v>
+        <v>0.07919857939596005</v>
       </c>
       <c r="T4">
-        <v>0.6459806821991591</v>
+        <v>0.6510004771704003</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>139.4390197847228</v>
+        <v>92.95934652314854</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07795437201408124</v>
+        <v>0.07779201843218178</v>
       </c>
       <c r="C5">
-        <v>3174.01992553058</v>
+        <v>3142.086820009516</v>
       </c>
       <c r="D5">
-        <v>3225.87292553058</v>
+        <v>3227.290820009517</v>
       </c>
       <c r="E5">
-        <v>-2199.347</v>
+        <v>-2165.996</v>
       </c>
       <c r="F5">
-        <v>100.053</v>
+        <v>133.404</v>
       </c>
       <c r="G5">
         <v>48.2</v>
@@ -1703,28 +1703,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M5">
-        <v>5.0326659</v>
+        <v>6.710221200000001</v>
       </c>
       <c r="N5">
-        <v>462.8006674333333</v>
+        <v>461.1231121333333</v>
       </c>
       <c r="O5">
-        <v>115.7001668583333</v>
+        <v>115.2807780333333</v>
       </c>
       <c r="P5">
-        <v>347.100500575</v>
+        <v>345.8423341</v>
       </c>
       <c r="Q5">
-        <v>828.100500575</v>
+        <v>826.8423341</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07919857939596005</v>
+        <v>0.0794614775335227</v>
       </c>
       <c r="T5">
-        <v>0.6510004771704003</v>
+        <v>0.6561248512035427</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.95934652314854</v>
+        <v>69.7195098923614</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07779201843218178</v>
+        <v>0.07762966485028236</v>
       </c>
       <c r="C6">
-        <v>3142.086820009516</v>
+        <v>3110.154961474213</v>
       </c>
       <c r="D6">
-        <v>3227.290820009517</v>
+        <v>3228.709961474213</v>
       </c>
       <c r="E6">
-        <v>-2165.996</v>
+        <v>-2132.645</v>
       </c>
       <c r="F6">
-        <v>133.404</v>
+        <v>166.755</v>
       </c>
       <c r="G6">
         <v>48.2</v>
@@ -1785,28 +1785,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M6">
-        <v>6.710221200000001</v>
+        <v>8.387776500000001</v>
       </c>
       <c r="N6">
-        <v>461.1231121333333</v>
+        <v>459.4455568333333</v>
       </c>
       <c r="O6">
-        <v>115.2807780333333</v>
+        <v>114.8613892083333</v>
       </c>
       <c r="P6">
-        <v>345.8423341</v>
+        <v>344.584167625</v>
       </c>
       <c r="Q6">
-        <v>826.8423341</v>
+        <v>825.584167625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0794614775335227</v>
+        <v>0.07972991036871827</v>
       </c>
       <c r="T6">
-        <v>0.6561248512035427</v>
+        <v>0.6613571067952775</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.7195098923614</v>
+        <v>55.77560791388913</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07762966485028236</v>
+        <v>0.0774673112683829</v>
       </c>
       <c r="C7">
-        <v>3110.154961474213</v>
+        <v>3078.224351570409</v>
       </c>
       <c r="D7">
-        <v>3228.709961474213</v>
+        <v>3230.130351570409</v>
       </c>
       <c r="E7">
-        <v>-2132.645</v>
+        <v>-2099.294</v>
       </c>
       <c r="F7">
-        <v>166.755</v>
+        <v>200.1060000000001</v>
       </c>
       <c r="G7">
         <v>48.2</v>
@@ -1867,28 +1867,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M7">
-        <v>8.387776500000001</v>
+        <v>10.0653318</v>
       </c>
       <c r="N7">
-        <v>459.4455568333333</v>
+        <v>457.7680015333332</v>
       </c>
       <c r="O7">
-        <v>114.8613892083333</v>
+        <v>114.4420003833333</v>
       </c>
       <c r="P7">
-        <v>344.584167625</v>
+        <v>343.3260011499999</v>
       </c>
       <c r="Q7">
-        <v>825.584167625</v>
+        <v>824.3260011499999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07972991036871827</v>
+        <v>0.08000405454083287</v>
       </c>
       <c r="T7">
-        <v>0.6613571067952775</v>
+        <v>0.6667006869740705</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.77560791388913</v>
+        <v>46.47967326157426</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0774673112683829</v>
+        <v>0.07730495768648345</v>
       </c>
       <c r="C8">
-        <v>3078.224351570409</v>
+        <v>3046.294991946744</v>
       </c>
       <c r="D8">
-        <v>3230.130351570409</v>
+        <v>3231.551991946744</v>
       </c>
       <c r="E8">
-        <v>-2099.294</v>
+        <v>-2065.943</v>
       </c>
       <c r="F8">
-        <v>200.106</v>
+        <v>233.457</v>
       </c>
       <c r="G8">
         <v>48.2</v>
@@ -1949,28 +1949,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M8">
-        <v>10.0653318</v>
+        <v>11.7428871</v>
       </c>
       <c r="N8">
-        <v>457.7680015333332</v>
+        <v>456.0904462333332</v>
       </c>
       <c r="O8">
-        <v>114.4420003833333</v>
+        <v>114.0226115583333</v>
       </c>
       <c r="P8">
-        <v>343.3260011499999</v>
+        <v>342.0678346749999</v>
       </c>
       <c r="Q8">
-        <v>824.3260011499999</v>
+        <v>823.0678346749999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08000405454083287</v>
+        <v>0.08028409428654135</v>
       </c>
       <c r="T8">
-        <v>0.6667006869740705</v>
+        <v>0.6721591828556331</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.47967326157427</v>
+        <v>39.83971993849224</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07730495768648345</v>
+        <v>0.07714260410458401</v>
       </c>
       <c r="C9">
-        <v>3046.294991946744</v>
+        <v>3014.366884254757</v>
       </c>
       <c r="D9">
-        <v>3231.551991946744</v>
+        <v>3232.974884254757</v>
       </c>
       <c r="E9">
-        <v>-2065.943</v>
+        <v>-2032.592</v>
       </c>
       <c r="F9">
-        <v>233.4570000000001</v>
+        <v>266.808</v>
       </c>
       <c r="G9">
         <v>48.2</v>
@@ -2031,28 +2031,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M9">
-        <v>11.7428871</v>
+        <v>13.4204424</v>
       </c>
       <c r="N9">
-        <v>456.0904462333332</v>
+        <v>454.4128909333332</v>
       </c>
       <c r="O9">
-        <v>114.0226115583333</v>
+        <v>113.6032227333333</v>
       </c>
       <c r="P9">
-        <v>342.0678346749999</v>
+        <v>340.8096681999999</v>
       </c>
       <c r="Q9">
-        <v>823.0678346749999</v>
+        <v>821.8096681999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08028409428654135</v>
+        <v>0.08057022185280871</v>
       </c>
       <c r="T9">
-        <v>0.6721591828556331</v>
+        <v>0.6777363416911431</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.83971993849222</v>
+        <v>34.8597549461807</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07714260410458401</v>
+        <v>0.07698025052268456</v>
       </c>
       <c r="C10">
-        <v>3014.366884254757</v>
+        <v>2982.440030148902</v>
       </c>
       <c r="D10">
-        <v>3232.974884254757</v>
+        <v>3234.399030148903</v>
       </c>
       <c r="E10">
-        <v>-2032.592</v>
+        <v>-1999.241</v>
       </c>
       <c r="F10">
-        <v>266.808</v>
+        <v>300.159</v>
       </c>
       <c r="G10">
         <v>48.2</v>
@@ -2113,28 +2113,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M10">
-        <v>13.4204424</v>
+        <v>15.0979977</v>
       </c>
       <c r="N10">
-        <v>454.4128909333332</v>
+        <v>452.7353356333332</v>
       </c>
       <c r="O10">
-        <v>113.6032227333333</v>
+        <v>113.1838339083333</v>
       </c>
       <c r="P10">
-        <v>340.8096681999999</v>
+        <v>339.5515017249999</v>
       </c>
       <c r="Q10">
-        <v>821.8096681999999</v>
+        <v>820.551501725</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08057022185280871</v>
+        <v>0.08086263793701599</v>
       </c>
       <c r="T10">
-        <v>0.6777363416911431</v>
+        <v>0.6834360754461144</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.8597549461807</v>
+        <v>30.98644884104951</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07698025052268456</v>
+        <v>0.07681789694078511</v>
       </c>
       <c r="C11">
-        <v>2982.440030148902</v>
+        <v>2950.514431286546</v>
       </c>
       <c r="D11">
-        <v>3234.399030148903</v>
+        <v>3235.824431286546</v>
       </c>
       <c r="E11">
-        <v>-1999.241</v>
+        <v>-1965.89</v>
       </c>
       <c r="F11">
-        <v>300.159</v>
+        <v>333.51</v>
       </c>
       <c r="G11">
         <v>48.2</v>
@@ -2195,28 +2195,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M11">
-        <v>15.0979977</v>
+        <v>16.775553</v>
       </c>
       <c r="N11">
-        <v>452.7353356333332</v>
+        <v>451.0577803333333</v>
       </c>
       <c r="O11">
-        <v>113.1838339083333</v>
+        <v>112.7644450833333</v>
       </c>
       <c r="P11">
-        <v>339.5515017249999</v>
+        <v>338.2933352499999</v>
       </c>
       <c r="Q11">
-        <v>820.551501725</v>
+        <v>819.2933352499999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08086263793701599</v>
+        <v>0.0811615521564279</v>
       </c>
       <c r="T11">
-        <v>0.6834360754461144</v>
+        <v>0.6892624699511963</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.98644884104951</v>
+        <v>27.88780395694457</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07681789694078511</v>
+        <v>0.07665554335888566</v>
       </c>
       <c r="C12">
-        <v>2950.514431286546</v>
+        <v>2918.59008932798</v>
       </c>
       <c r="D12">
-        <v>3235.824431286546</v>
+        <v>3237.25108932798</v>
       </c>
       <c r="E12">
-        <v>-1965.89</v>
+        <v>-1932.539</v>
       </c>
       <c r="F12">
-        <v>333.51</v>
+        <v>366.861</v>
       </c>
       <c r="G12">
         <v>48.2</v>
@@ -2277,28 +2277,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M12">
-        <v>16.775553</v>
+        <v>18.4531083</v>
       </c>
       <c r="N12">
-        <v>451.0577803333333</v>
+        <v>449.3802250333333</v>
       </c>
       <c r="O12">
-        <v>112.7644450833333</v>
+        <v>112.3450562583333</v>
       </c>
       <c r="P12">
-        <v>338.2933352499999</v>
+        <v>337.0351687749999</v>
       </c>
       <c r="Q12">
-        <v>819.2933352499999</v>
+        <v>818.0351687749999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0811615521564279</v>
+        <v>0.08146718354930974</v>
       </c>
       <c r="T12">
-        <v>0.6892624699511963</v>
+        <v>0.6952197946698757</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.88780395694456</v>
+        <v>25.35254905176778</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07665554335888566</v>
+        <v>0.07649318977698621</v>
       </c>
       <c r="C13">
-        <v>2918.59008932798</v>
+        <v>2886.667005936423</v>
       </c>
       <c r="D13">
-        <v>3237.25108932798</v>
+        <v>3238.679005936423</v>
       </c>
       <c r="E13">
-        <v>-1932.539</v>
+        <v>-1899.188</v>
       </c>
       <c r="F13">
-        <v>366.861</v>
+        <v>400.212</v>
       </c>
       <c r="G13">
         <v>48.2</v>
@@ -2359,28 +2359,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M13">
-        <v>18.4531083</v>
+        <v>20.1306636</v>
       </c>
       <c r="N13">
-        <v>449.3802250333333</v>
+        <v>447.7026697333333</v>
       </c>
       <c r="O13">
-        <v>112.3450562583333</v>
+        <v>111.9256674333333</v>
       </c>
       <c r="P13">
-        <v>337.0351687749999</v>
+        <v>335.7770022999999</v>
       </c>
       <c r="Q13">
-        <v>818.0351687749999</v>
+        <v>816.7770022999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08146718354930974</v>
+        <v>0.0817797611102116</v>
       </c>
       <c r="T13">
-        <v>0.6952197946698757</v>
+        <v>0.7013125131321614</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.35254905176778</v>
+        <v>23.23983663078713</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07649318977698621</v>
+        <v>0.07633083619508677</v>
       </c>
       <c r="C14">
-        <v>2886.667005936423</v>
+        <v>2854.745182778032</v>
       </c>
       <c r="D14">
-        <v>3238.679005936423</v>
+        <v>3240.108182778033</v>
       </c>
       <c r="E14">
-        <v>-1899.188</v>
+        <v>-1865.837</v>
       </c>
       <c r="F14">
-        <v>400.212</v>
+        <v>433.563</v>
       </c>
       <c r="G14">
         <v>48.2</v>
@@ -2441,28 +2441,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M14">
-        <v>20.1306636</v>
+        <v>21.8082189</v>
       </c>
       <c r="N14">
-        <v>447.7026697333333</v>
+        <v>446.0251144333333</v>
       </c>
       <c r="O14">
-        <v>111.9256674333333</v>
+        <v>111.5062786083333</v>
       </c>
       <c r="P14">
-        <v>335.7770022999999</v>
+        <v>334.5188358249999</v>
       </c>
       <c r="Q14">
-        <v>816.7770022999999</v>
+        <v>815.518835825</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0817797611102116</v>
+        <v>0.08209952436216869</v>
       </c>
       <c r="T14">
-        <v>0.7013125131321614</v>
+        <v>0.7075452940878328</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.23983663078713</v>
+        <v>21.45215688995736</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07633083619508677</v>
+        <v>0.0761684826131873</v>
       </c>
       <c r="C15">
-        <v>2854.745182778032</v>
+        <v>2822.824621521906</v>
       </c>
       <c r="D15">
-        <v>3240.108182778033</v>
+        <v>3241.538621521906</v>
       </c>
       <c r="E15">
-        <v>-1865.837</v>
+        <v>-1832.486</v>
       </c>
       <c r="F15">
-        <v>433.563</v>
+        <v>466.9140000000001</v>
       </c>
       <c r="G15">
         <v>48.2</v>
@@ -2523,28 +2523,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M15">
-        <v>21.8082189</v>
+        <v>23.48577420000001</v>
       </c>
       <c r="N15">
-        <v>446.0251144333333</v>
+        <v>444.3475591333333</v>
       </c>
       <c r="O15">
-        <v>111.5062786083333</v>
+        <v>111.0868897833333</v>
       </c>
       <c r="P15">
-        <v>334.5188358249999</v>
+        <v>333.2606693499999</v>
       </c>
       <c r="Q15">
-        <v>815.518835825</v>
+        <v>814.2606693499999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08209952436216869</v>
+        <v>0.08242672396882245</v>
       </c>
       <c r="T15">
-        <v>0.7075452940878328</v>
+        <v>0.7139230234378224</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.45215688995736</v>
+        <v>19.91985996924612</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0761684826131873</v>
+        <v>0.07600612903128787</v>
       </c>
       <c r="C16">
-        <v>2822.824621521906</v>
+        <v>2790.905323840091</v>
       </c>
       <c r="D16">
-        <v>3241.538621521906</v>
+        <v>3242.970323840091</v>
       </c>
       <c r="E16">
-        <v>-1832.486</v>
+        <v>-1799.135</v>
       </c>
       <c r="F16">
-        <v>466.9140000000001</v>
+        <v>500.2650000000002</v>
       </c>
       <c r="G16">
         <v>48.2</v>
@@ -2605,28 +2605,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M16">
-        <v>23.48577420000001</v>
+        <v>25.16332950000001</v>
       </c>
       <c r="N16">
-        <v>444.3475591333333</v>
+        <v>442.6700038333332</v>
       </c>
       <c r="O16">
-        <v>111.0868897833333</v>
+        <v>110.6675009583333</v>
       </c>
       <c r="P16">
-        <v>333.2606693499999</v>
+        <v>332.0025028749999</v>
       </c>
       <c r="Q16">
-        <v>814.2606693499999</v>
+        <v>813.0025028749999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08242672396882245</v>
+        <v>0.08276162238975043</v>
       </c>
       <c r="T16">
-        <v>0.7139230234378224</v>
+        <v>0.7204508170078117</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.91985996924612</v>
+        <v>18.5918693046297</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07600612903128787</v>
+        <v>0.07584377544938842</v>
       </c>
       <c r="C17">
-        <v>2790.905323840091</v>
+        <v>2758.98729140759</v>
       </c>
       <c r="D17">
-        <v>3242.970323840091</v>
+        <v>3244.40329140759</v>
       </c>
       <c r="E17">
-        <v>-1799.135</v>
+        <v>-1765.784</v>
       </c>
       <c r="F17">
-        <v>500.265</v>
+        <v>533.6160000000001</v>
       </c>
       <c r="G17">
         <v>48.2</v>
@@ -2687,28 +2687,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M17">
-        <v>25.1633295</v>
+        <v>26.8408848</v>
       </c>
       <c r="N17">
-        <v>442.6700038333333</v>
+        <v>440.9924485333332</v>
       </c>
       <c r="O17">
-        <v>110.6675009583333</v>
+        <v>110.2481121333333</v>
       </c>
       <c r="P17">
-        <v>332.0025028749999</v>
+        <v>330.7443364</v>
       </c>
       <c r="Q17">
-        <v>813.0025028749999</v>
+        <v>811.7443364</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08276162238975043</v>
+        <v>0.08310449458260526</v>
       </c>
       <c r="T17">
-        <v>0.7204508170078117</v>
+        <v>0.7271340342342292</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.59186930462971</v>
+        <v>17.42987747309035</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07584377544938842</v>
+        <v>0.07568142186748895</v>
       </c>
       <c r="C18">
-        <v>2758.98729140759</v>
+        <v>2727.070525902366</v>
       </c>
       <c r="D18">
-        <v>3244.40329140759</v>
+        <v>3245.837525902366</v>
       </c>
       <c r="E18">
-        <v>-1765.784</v>
+        <v>-1732.433</v>
       </c>
       <c r="F18">
-        <v>533.6160000000001</v>
+        <v>566.9670000000001</v>
       </c>
       <c r="G18">
         <v>48.2</v>
@@ -2769,28 +2769,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M18">
-        <v>26.8408848</v>
+        <v>28.5184401</v>
       </c>
       <c r="N18">
-        <v>440.9924485333332</v>
+        <v>439.3148932333332</v>
       </c>
       <c r="O18">
-        <v>110.2481121333333</v>
+        <v>109.8287233083333</v>
       </c>
       <c r="P18">
-        <v>330.7443364</v>
+        <v>329.4861699249999</v>
       </c>
       <c r="Q18">
-        <v>811.7443364</v>
+        <v>810.4861699249999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08310449458260526</v>
+        <v>0.0834556287560108</v>
       </c>
       <c r="T18">
-        <v>0.7271340342342292</v>
+        <v>0.7339782928395966</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.42987747309035</v>
+        <v>16.40459056290857</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07568142186748895</v>
+        <v>0.07551906828558952</v>
       </c>
       <c r="C19">
-        <v>2727.070525902366</v>
+        <v>2695.155029005353</v>
       </c>
       <c r="D19">
-        <v>3245.837525902366</v>
+        <v>3247.273029005353</v>
       </c>
       <c r="E19">
-        <v>-1732.433</v>
+        <v>-1699.082</v>
       </c>
       <c r="F19">
-        <v>566.9670000000001</v>
+        <v>600.3180000000001</v>
       </c>
       <c r="G19">
         <v>48.2</v>
@@ -2851,28 +2851,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M19">
-        <v>28.5184401</v>
+        <v>30.1959954</v>
       </c>
       <c r="N19">
-        <v>439.3148932333332</v>
+        <v>437.6373379333332</v>
       </c>
       <c r="O19">
-        <v>109.8287233083333</v>
+        <v>109.4093344833333</v>
       </c>
       <c r="P19">
-        <v>329.4861699249999</v>
+        <v>328.22800345</v>
       </c>
       <c r="Q19">
-        <v>810.4861699249999</v>
+        <v>809.22800345</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0834556287560108</v>
+        <v>0.08381532717754819</v>
       </c>
       <c r="T19">
-        <v>0.7339782928395966</v>
+        <v>0.7409894845816801</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.40459056290857</v>
+        <v>15.49322442052476</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07551906828558953</v>
+        <v>0.07535671470369007</v>
       </c>
       <c r="C20">
-        <v>2695.155029005352</v>
+        <v>2663.240802400458</v>
       </c>
       <c r="D20">
-        <v>3247.273029005353</v>
+        <v>3248.709802400459</v>
       </c>
       <c r="E20">
-        <v>-1699.082</v>
+        <v>-1665.731</v>
       </c>
       <c r="F20">
-        <v>600.3180000000001</v>
+        <v>633.6690000000001</v>
       </c>
       <c r="G20">
         <v>48.2</v>
@@ -2933,28 +2933,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M20">
-        <v>30.1959954</v>
+        <v>31.8735507</v>
       </c>
       <c r="N20">
-        <v>437.6373379333332</v>
+        <v>435.9597826333332</v>
       </c>
       <c r="O20">
-        <v>109.4093344833333</v>
+        <v>108.9899456583333</v>
       </c>
       <c r="P20">
-        <v>328.22800345</v>
+        <v>326.9698369749999</v>
       </c>
       <c r="Q20">
-        <v>809.22800345</v>
+        <v>807.9698369749999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08381532717754819</v>
+        <v>0.08418390704159268</v>
       </c>
       <c r="T20">
-        <v>0.7409894845816801</v>
+        <v>0.7481737921692475</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.49322442052476</v>
+        <v>14.67779155628661</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07535671470369007</v>
+        <v>0.07519436112179061</v>
       </c>
       <c r="C21">
-        <v>2663.240802400458</v>
+        <v>2631.32784777457</v>
       </c>
       <c r="D21">
-        <v>3248.709802400459</v>
+        <v>3250.14784777457</v>
       </c>
       <c r="E21">
-        <v>-1665.731</v>
+        <v>-1632.38</v>
       </c>
       <c r="F21">
-        <v>633.6690000000001</v>
+        <v>667.0200000000001</v>
       </c>
       <c r="G21">
         <v>48.2</v>
@@ -3015,28 +3015,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M21">
-        <v>31.8735507</v>
+        <v>33.551106</v>
       </c>
       <c r="N21">
-        <v>435.9597826333332</v>
+        <v>434.2822273333333</v>
       </c>
       <c r="O21">
-        <v>108.9899456583333</v>
+        <v>108.5705568333333</v>
       </c>
       <c r="P21">
-        <v>326.9698369749999</v>
+        <v>325.7116705</v>
       </c>
       <c r="Q21">
-        <v>807.9698369749999</v>
+        <v>806.7116705</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08418390704159268</v>
+        <v>0.08456170140223826</v>
       </c>
       <c r="T21">
-        <v>0.7481737921692475</v>
+        <v>0.7555377074465037</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.67779155628661</v>
+        <v>13.94390197847228</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07519436112179061</v>
+        <v>0.07503200753989117</v>
       </c>
       <c r="C22">
-        <v>2631.32784777457</v>
+        <v>2599.416166817567</v>
       </c>
       <c r="D22">
-        <v>3250.14784777457</v>
+        <v>3251.587166817567</v>
       </c>
       <c r="E22">
-        <v>-1632.38</v>
+        <v>-1599.029</v>
       </c>
       <c r="F22">
-        <v>667.0200000000001</v>
+        <v>700.3710000000001</v>
       </c>
       <c r="G22">
         <v>48.2</v>
@@ -3097,28 +3097,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M22">
-        <v>33.551106</v>
+        <v>35.22866130000001</v>
       </c>
       <c r="N22">
-        <v>434.2822273333333</v>
+        <v>432.6046720333333</v>
       </c>
       <c r="O22">
-        <v>108.5705568333333</v>
+        <v>108.1511680083333</v>
       </c>
       <c r="P22">
-        <v>325.7116705</v>
+        <v>324.4535040249999</v>
       </c>
       <c r="Q22">
-        <v>806.7116705</v>
+        <v>805.4535040249999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08456170140223826</v>
+        <v>0.08494906017707743</v>
       </c>
       <c r="T22">
-        <v>0.7555377074465037</v>
+        <v>0.7630880509586273</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.94390197847228</v>
+        <v>13.27990664616408</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07503200753989117</v>
+        <v>0.07511715395799172</v>
       </c>
       <c r="C23">
-        <v>2599.416166817567</v>
+        <v>2565.310156286205</v>
       </c>
       <c r="D23">
-        <v>3251.587166817567</v>
+        <v>3250.832156286205</v>
       </c>
       <c r="E23">
-        <v>-1599.029</v>
+        <v>-1565.678</v>
       </c>
       <c r="F23">
-        <v>700.3710000000001</v>
+        <v>733.7220000000001</v>
       </c>
       <c r="G23">
         <v>48.2</v>
@@ -3179,45 +3179,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M23">
-        <v>35.22866130000001</v>
+        <v>38.0067996</v>
       </c>
       <c r="N23">
-        <v>432.6046720333333</v>
+        <v>429.8265337333332</v>
       </c>
       <c r="O23">
-        <v>108.1511680083333</v>
+        <v>107.4566334333333</v>
       </c>
       <c r="P23">
-        <v>324.4535040249999</v>
+        <v>322.3699002999999</v>
       </c>
       <c r="Q23">
-        <v>805.4535040249999</v>
+        <v>803.3699002999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08494906017707743</v>
+        <v>0.08534635122819451</v>
       </c>
       <c r="T23">
-        <v>0.7630880509586273</v>
+        <v>0.7708319930223438</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.27990664616408</v>
+        <v>12.30920093922702</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07511715395799172</v>
+        <v>0.07496605037609227</v>
       </c>
       <c r="C24">
-        <v>2565.310156286205</v>
+        <v>2533.299263443215</v>
       </c>
       <c r="D24">
-        <v>3250.832156286205</v>
+        <v>3252.172263443215</v>
       </c>
       <c r="E24">
-        <v>-1565.678</v>
+        <v>-1532.327</v>
       </c>
       <c r="F24">
-        <v>733.7220000000001</v>
+        <v>767.0730000000001</v>
       </c>
       <c r="G24">
         <v>48.2</v>
@@ -3261,28 +3261,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M24">
-        <v>38.0067996</v>
+        <v>39.7343814</v>
       </c>
       <c r="N24">
-        <v>429.8265337333332</v>
+        <v>428.0989519333332</v>
       </c>
       <c r="O24">
-        <v>107.4566334333333</v>
+        <v>107.0247379833333</v>
       </c>
       <c r="P24">
-        <v>322.3699002999999</v>
+        <v>321.0742139499999</v>
       </c>
       <c r="Q24">
-        <v>803.3699002999999</v>
+        <v>802.0742139499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08534635122819451</v>
+        <v>0.08575396152739256</v>
       </c>
       <c r="T24">
-        <v>0.7708319930223438</v>
+        <v>0.7787770764383648</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.30920093922702</v>
+        <v>11.77401828969541</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07496605037609227</v>
+        <v>0.07481494679419283</v>
       </c>
       <c r="C25">
-        <v>2533.299263443215</v>
+        <v>2501.28947593433</v>
       </c>
       <c r="D25">
-        <v>3252.172263443215</v>
+        <v>3253.51347593433</v>
       </c>
       <c r="E25">
-        <v>-1532.327</v>
+        <v>-1498.976</v>
       </c>
       <c r="F25">
-        <v>767.0730000000001</v>
+        <v>800.4240000000002</v>
       </c>
       <c r="G25">
         <v>48.2</v>
@@ -3343,28 +3343,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M25">
-        <v>39.7343814</v>
+        <v>41.46196320000001</v>
       </c>
       <c r="N25">
-        <v>428.0989519333332</v>
+        <v>426.3713701333332</v>
       </c>
       <c r="O25">
-        <v>107.0247379833333</v>
+        <v>106.5928425333333</v>
       </c>
       <c r="P25">
-        <v>321.0742139499999</v>
+        <v>319.7785276</v>
       </c>
       <c r="Q25">
-        <v>802.0742139499999</v>
+        <v>800.7785276</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08575396152739256</v>
+        <v>0.08617229841341162</v>
       </c>
       <c r="T25">
-        <v>0.7787770764383648</v>
+        <v>0.7869312409969126</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.77401828969541</v>
+        <v>11.28343419429144</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07481494679419283</v>
+        <v>0.07466384321229337</v>
       </c>
       <c r="C26">
-        <v>2501.28947593433</v>
+        <v>2469.28079512765</v>
       </c>
       <c r="D26">
-        <v>3253.51347593433</v>
+        <v>3254.855795127651</v>
       </c>
       <c r="E26">
-        <v>-1498.976</v>
+        <v>-1465.625</v>
       </c>
       <c r="F26">
-        <v>800.4240000000001</v>
+        <v>833.7750000000001</v>
       </c>
       <c r="G26">
         <v>48.2</v>
@@ -3425,28 +3425,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M26">
-        <v>41.46196320000001</v>
+        <v>43.189545</v>
       </c>
       <c r="N26">
-        <v>426.3713701333332</v>
+        <v>424.6437883333332</v>
       </c>
       <c r="O26">
-        <v>106.5928425333333</v>
+        <v>106.1609470833333</v>
       </c>
       <c r="P26">
-        <v>319.7785276</v>
+        <v>318.4828412499999</v>
       </c>
       <c r="Q26">
-        <v>800.7785276</v>
+        <v>799.4828412499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08617229841341162</v>
+        <v>0.08660179094972451</v>
       </c>
       <c r="T26">
-        <v>0.7869312409969126</v>
+        <v>0.7953028499436882</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.28343419429144</v>
+        <v>10.83209682651978</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07466384321229337</v>
+        <v>0.07451273963039391</v>
       </c>
       <c r="C27">
-        <v>2469.28079512765</v>
+        <v>2437.273222393535</v>
       </c>
       <c r="D27">
-        <v>3254.855795127651</v>
+        <v>3256.199222393535</v>
       </c>
       <c r="E27">
-        <v>-1465.625</v>
+        <v>-1432.274</v>
       </c>
       <c r="F27">
-        <v>833.7750000000001</v>
+        <v>867.1260000000001</v>
       </c>
       <c r="G27">
         <v>48.2</v>
@@ -3507,28 +3507,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M27">
-        <v>43.189545</v>
+        <v>44.91712680000001</v>
       </c>
       <c r="N27">
-        <v>424.6437883333332</v>
+        <v>422.9162065333333</v>
       </c>
       <c r="O27">
-        <v>106.1609470833333</v>
+        <v>105.7290516333333</v>
       </c>
       <c r="P27">
-        <v>318.4828412499999</v>
+        <v>317.1871548999999</v>
       </c>
       <c r="Q27">
-        <v>799.4828412499999</v>
+        <v>798.1871549</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08660179094972451</v>
+        <v>0.08704289139242422</v>
       </c>
       <c r="T27">
-        <v>0.7953028499436882</v>
+        <v>0.8039007185917281</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.83209682651978</v>
+        <v>10.41547771780748</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07451273963039391</v>
+        <v>0.07436163604849448</v>
       </c>
       <c r="C28">
-        <v>2437.273222393535</v>
+        <v>2405.266759104607</v>
       </c>
       <c r="D28">
-        <v>3256.199222393535</v>
+        <v>3257.543759104607</v>
       </c>
       <c r="E28">
-        <v>-1432.274</v>
+        <v>-1398.923</v>
       </c>
       <c r="F28">
-        <v>867.1260000000001</v>
+        <v>900.4770000000002</v>
       </c>
       <c r="G28">
         <v>48.2</v>
@@ -3589,28 +3589,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M28">
-        <v>44.91712680000001</v>
+        <v>46.64470860000001</v>
       </c>
       <c r="N28">
-        <v>422.9162065333333</v>
+        <v>421.1886247333333</v>
       </c>
       <c r="O28">
-        <v>105.7290516333333</v>
+        <v>105.2971561833333</v>
       </c>
       <c r="P28">
-        <v>317.1871548999999</v>
+        <v>315.89146855</v>
       </c>
       <c r="Q28">
-        <v>798.1871549</v>
+        <v>796.8914685499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08704289139242422</v>
+        <v>0.08749607677875956</v>
       </c>
       <c r="T28">
-        <v>0.8039007185917281</v>
+        <v>0.8127341452849197</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.41547771780748</v>
+        <v>10.02971928381461</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07436163604849448</v>
+        <v>0.07456753246659503</v>
       </c>
       <c r="C29">
-        <v>2405.266759104607</v>
+        <v>2370.083943723959</v>
       </c>
       <c r="D29">
-        <v>3257.543759104607</v>
+        <v>3255.71194372396</v>
       </c>
       <c r="E29">
-        <v>-1398.923</v>
+        <v>-1365.572</v>
       </c>
       <c r="F29">
-        <v>900.4770000000002</v>
+        <v>933.8280000000002</v>
       </c>
       <c r="G29">
         <v>48.2</v>
@@ -3671,45 +3671,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M29">
-        <v>46.64470860000001</v>
+        <v>49.95979800000001</v>
       </c>
       <c r="N29">
-        <v>421.1886247333333</v>
+        <v>417.8735353333333</v>
       </c>
       <c r="O29">
-        <v>105.2971561833333</v>
+        <v>104.4683838333333</v>
       </c>
       <c r="P29">
-        <v>315.89146855</v>
+        <v>313.4051515</v>
       </c>
       <c r="Q29">
-        <v>796.8914685499999</v>
+        <v>794.4051515</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08749607677875956</v>
+        <v>0.08796185064804865</v>
       </c>
       <c r="T29">
-        <v>0.8127341452849197</v>
+        <v>0.8218129449418111</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>10.02971928381461</v>
+        <v>9.364195854701679</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07456753246659503</v>
+        <v>0.07442917888469558</v>
       </c>
       <c r="C30">
-        <v>2370.083943723959</v>
+        <v>2337.963618121395</v>
       </c>
       <c r="D30">
-        <v>3255.71194372396</v>
+        <v>3256.942618121395</v>
       </c>
       <c r="E30">
-        <v>-1365.572</v>
+        <v>-1332.221</v>
       </c>
       <c r="F30">
-        <v>933.8280000000002</v>
+        <v>967.1790000000002</v>
       </c>
       <c r="G30">
         <v>48.2</v>
@@ -3753,28 +3753,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M30">
-        <v>49.95979800000001</v>
+        <v>51.74407650000001</v>
       </c>
       <c r="N30">
-        <v>417.8735353333333</v>
+        <v>416.0892568333333</v>
       </c>
       <c r="O30">
-        <v>104.4683838333333</v>
+        <v>104.0223142083333</v>
       </c>
       <c r="P30">
-        <v>313.4051515</v>
+        <v>312.0669426249999</v>
       </c>
       <c r="Q30">
-        <v>794.4051515</v>
+        <v>793.0669426249999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08796185064804865</v>
+        <v>0.08844074490802194</v>
       </c>
       <c r="T30">
-        <v>0.8218129449418111</v>
+        <v>0.8311474854341079</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.364195854701679</v>
+        <v>9.041292549367137</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07442917888469558</v>
+        <v>0.07429082530279613</v>
       </c>
       <c r="C31">
-        <v>2337.963618121395</v>
+        <v>2305.844223272057</v>
       </c>
       <c r="D31">
-        <v>3256.942618121395</v>
+        <v>3258.174223272057</v>
       </c>
       <c r="E31">
-        <v>-1332.221</v>
+        <v>-1298.87</v>
       </c>
       <c r="F31">
-        <v>967.1790000000001</v>
+        <v>1000.53</v>
       </c>
       <c r="G31">
         <v>48.2</v>
@@ -3835,28 +3835,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M31">
-        <v>51.74407650000001</v>
+        <v>53.528355</v>
       </c>
       <c r="N31">
-        <v>416.0892568333333</v>
+        <v>414.3049783333332</v>
       </c>
       <c r="O31">
-        <v>104.0223142083333</v>
+        <v>103.5762445833333</v>
       </c>
       <c r="P31">
-        <v>312.0669426249999</v>
+        <v>310.7287337499999</v>
       </c>
       <c r="Q31">
-        <v>793.0669426249999</v>
+        <v>791.7287337499999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08844074490802194</v>
+        <v>0.08893332186113732</v>
       </c>
       <c r="T31">
-        <v>0.8311474854341079</v>
+        <v>0.8407487270833275</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.041292549367137</v>
+        <v>8.739916131054899</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07429082530279613</v>
+        <v>0.07415247172089667</v>
       </c>
       <c r="C32">
-        <v>2305.844223272057</v>
+        <v>2273.725760232232</v>
       </c>
       <c r="D32">
-        <v>3258.174223272057</v>
+        <v>3259.406760232232</v>
       </c>
       <c r="E32">
-        <v>-1298.87</v>
+        <v>-1265.519</v>
       </c>
       <c r="F32">
-        <v>1000.53</v>
+        <v>1033.881</v>
       </c>
       <c r="G32">
         <v>48.2</v>
@@ -3917,28 +3917,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M32">
-        <v>53.528355</v>
+        <v>55.3126335</v>
       </c>
       <c r="N32">
-        <v>414.3049783333332</v>
+        <v>412.5206998333333</v>
       </c>
       <c r="O32">
-        <v>103.5762445833333</v>
+        <v>103.1301749583333</v>
       </c>
       <c r="P32">
-        <v>310.7287337499999</v>
+        <v>309.3905248749999</v>
       </c>
       <c r="Q32">
-        <v>791.7287337499999</v>
+        <v>790.390524875</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08893332186113732</v>
+        <v>0.08944017640709663</v>
       </c>
       <c r="T32">
-        <v>0.8407487270833275</v>
+        <v>0.8506282655919447</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.739916131054899</v>
+        <v>8.457983352633775</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07415247172089667</v>
+        <v>0.07401411813899722</v>
       </c>
       <c r="C33">
-        <v>2273.725760232232</v>
+        <v>2241.608230059805</v>
       </c>
       <c r="D33">
-        <v>3259.406760232232</v>
+        <v>3260.640230059806</v>
       </c>
       <c r="E33">
-        <v>-1265.519</v>
+        <v>-1232.168</v>
       </c>
       <c r="F33">
-        <v>1033.881</v>
+        <v>1067.232</v>
       </c>
       <c r="G33">
         <v>48.2</v>
@@ -3999,28 +3999,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M33">
-        <v>55.3126335</v>
+        <v>57.09691200000001</v>
       </c>
       <c r="N33">
-        <v>412.5206998333333</v>
+        <v>410.7364213333332</v>
       </c>
       <c r="O33">
-        <v>103.1301749583333</v>
+        <v>102.6841053333333</v>
       </c>
       <c r="P33">
-        <v>309.3905248749999</v>
+        <v>308.0523159999999</v>
       </c>
       <c r="Q33">
-        <v>790.390524875</v>
+        <v>789.0523159999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08944017640709663</v>
+        <v>0.08996193843970181</v>
       </c>
       <c r="T33">
-        <v>0.8506282655919447</v>
+        <v>0.8607983787625801</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.457983352633775</v>
+        <v>8.193671372863967</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07401411813899722</v>
+        <v>0.07387576455709778</v>
       </c>
       <c r="C34">
-        <v>2241.608230059805</v>
+        <v>2209.491633814263</v>
       </c>
       <c r="D34">
-        <v>3260.640230059806</v>
+        <v>3261.874633814264</v>
       </c>
       <c r="E34">
-        <v>-1232.168</v>
+        <v>-1198.817</v>
       </c>
       <c r="F34">
-        <v>1067.232</v>
+        <v>1100.583</v>
       </c>
       <c r="G34">
         <v>48.2</v>
@@ -4081,28 +4081,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M34">
-        <v>57.09691200000001</v>
+        <v>58.8811905</v>
       </c>
       <c r="N34">
-        <v>410.7364213333332</v>
+        <v>408.9521428333333</v>
       </c>
       <c r="O34">
-        <v>102.6841053333333</v>
+        <v>102.2380357083333</v>
       </c>
       <c r="P34">
-        <v>308.0523159999999</v>
+        <v>306.7141071249999</v>
       </c>
       <c r="Q34">
-        <v>789.0523159999999</v>
+        <v>787.7141071249999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08996193843970181</v>
+        <v>0.0904992754583549</v>
       </c>
       <c r="T34">
-        <v>0.8607983787625801</v>
+        <v>0.8712720774009958</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.193671372863967</v>
+        <v>7.945378300959001</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07387576455709778</v>
+        <v>0.07373741097519834</v>
       </c>
       <c r="C35">
-        <v>2209.491633814263</v>
+        <v>2177.375972556698</v>
       </c>
       <c r="D35">
-        <v>3261.874633814264</v>
+        <v>3263.109972556698</v>
       </c>
       <c r="E35">
-        <v>-1198.817</v>
+        <v>-1165.466</v>
       </c>
       <c r="F35">
-        <v>1100.583</v>
+        <v>1133.934</v>
       </c>
       <c r="G35">
         <v>48.2</v>
@@ -4163,28 +4163,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M35">
-        <v>58.8811905</v>
+        <v>60.66546900000001</v>
       </c>
       <c r="N35">
-        <v>408.9521428333333</v>
+        <v>407.1678643333332</v>
       </c>
       <c r="O35">
-        <v>102.2380357083333</v>
+        <v>101.7919660833333</v>
       </c>
       <c r="P35">
-        <v>306.7141071249999</v>
+        <v>305.3758982499999</v>
       </c>
       <c r="Q35">
-        <v>787.7141071249999</v>
+        <v>786.3758982499999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0904992754583549</v>
+        <v>0.09105289541696718</v>
       </c>
       <c r="T35">
-        <v>0.8712720774009958</v>
+        <v>0.8820631608466361</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.945378300959001</v>
+        <v>7.71169070387197</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07373741097519834</v>
+        <v>0.07380905739329888</v>
       </c>
       <c r="C36">
-        <v>2177.375972556698</v>
+        <v>2143.385135458573</v>
       </c>
       <c r="D36">
-        <v>3263.109972556698</v>
+        <v>3262.470135458573</v>
       </c>
       <c r="E36">
-        <v>-1165.466</v>
+        <v>-1132.115</v>
       </c>
       <c r="F36">
-        <v>1133.934</v>
+        <v>1167.285</v>
       </c>
       <c r="G36">
         <v>48.2</v>
@@ -4245,45 +4245,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M36">
-        <v>60.66546900000001</v>
+        <v>63.38357550000002</v>
       </c>
       <c r="N36">
-        <v>407.1678643333332</v>
+        <v>404.4497578333333</v>
       </c>
       <c r="O36">
-        <v>101.7919660833333</v>
+        <v>101.1124394583333</v>
       </c>
       <c r="P36">
-        <v>305.3758982499999</v>
+        <v>303.3373183749999</v>
       </c>
       <c r="Q36">
-        <v>786.3758982499999</v>
+        <v>784.337318375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09105289541696718</v>
+        <v>0.09162354983584443</v>
       </c>
       <c r="T36">
-        <v>0.8820631608466361</v>
+        <v>0.8931862776290652</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.71169070387197</v>
+        <v>7.380986787867989</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07380905739329888</v>
+        <v>0.07367670381139943</v>
       </c>
       <c r="C37">
-        <v>2143.385135458573</v>
+        <v>2111.216313283012</v>
       </c>
       <c r="D37">
-        <v>3262.470135458573</v>
+        <v>3263.652313283012</v>
       </c>
       <c r="E37">
-        <v>-1132.115</v>
+        <v>-1098.764</v>
       </c>
       <c r="F37">
-        <v>1167.285</v>
+        <v>1200.636</v>
       </c>
       <c r="G37">
         <v>48.2</v>
@@ -4327,28 +4327,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M37">
-        <v>63.38357550000002</v>
+        <v>65.19453480000001</v>
       </c>
       <c r="N37">
-        <v>404.4497578333333</v>
+        <v>402.6387985333332</v>
       </c>
       <c r="O37">
-        <v>101.1124394583333</v>
+        <v>100.6596996333333</v>
       </c>
       <c r="P37">
-        <v>303.3373183749999</v>
+        <v>301.9790988999999</v>
       </c>
       <c r="Q37">
-        <v>784.337318375</v>
+        <v>782.9790988999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09162354983584443</v>
+        <v>0.09221203720531161</v>
       </c>
       <c r="T37">
-        <v>0.8931862776290652</v>
+        <v>0.9046569918109453</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.380986787867989</v>
+        <v>7.175959377093878</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07367670381139943</v>
+        <v>0.07354435022949998</v>
       </c>
       <c r="C38">
-        <v>2111.216313283012</v>
+        <v>2079.048348158055</v>
       </c>
       <c r="D38">
-        <v>3263.652313283012</v>
+        <v>3264.835348158056</v>
       </c>
       <c r="E38">
-        <v>-1098.764</v>
+        <v>-1065.413</v>
       </c>
       <c r="F38">
-        <v>1200.636</v>
+        <v>1233.987</v>
       </c>
       <c r="G38">
         <v>48.2</v>
@@ -4409,28 +4409,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M38">
-        <v>65.19453480000001</v>
+        <v>67.00549410000001</v>
       </c>
       <c r="N38">
-        <v>402.6387985333332</v>
+        <v>400.8278392333332</v>
       </c>
       <c r="O38">
-        <v>100.6596996333333</v>
+        <v>100.2069598083333</v>
       </c>
       <c r="P38">
-        <v>301.9790988999999</v>
+        <v>300.6208794249999</v>
       </c>
       <c r="Q38">
-        <v>782.9790988999999</v>
+        <v>781.6208794249999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09221203720531161</v>
+        <v>0.09281920671349203</v>
       </c>
       <c r="T38">
-        <v>0.9046569918109453</v>
+        <v>0.9164918556493931</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.175959377093878</v>
+        <v>6.982014529064315</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07354435022949998</v>
+        <v>0.07341199664760054</v>
       </c>
       <c r="C39">
-        <v>2079.048348158055</v>
+        <v>2046.881241016054</v>
       </c>
       <c r="D39">
-        <v>3264.835348158056</v>
+        <v>3266.019241016054</v>
       </c>
       <c r="E39">
-        <v>-1065.413</v>
+        <v>-1032.062</v>
       </c>
       <c r="F39">
-        <v>1233.987</v>
+        <v>1267.338</v>
       </c>
       <c r="G39">
         <v>48.2</v>
@@ -4491,28 +4491,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M39">
-        <v>67.00549410000001</v>
+        <v>68.81645340000001</v>
       </c>
       <c r="N39">
-        <v>400.8278392333332</v>
+        <v>399.0168799333333</v>
       </c>
       <c r="O39">
-        <v>100.2069598083333</v>
+        <v>99.75421998333331</v>
       </c>
       <c r="P39">
-        <v>300.6208794249999</v>
+        <v>299.2626599499999</v>
       </c>
       <c r="Q39">
-        <v>781.6208794249999</v>
+        <v>780.2626599499999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09281920671349203</v>
+        <v>0.09344596233483957</v>
       </c>
       <c r="T39">
-        <v>0.9164918556493931</v>
+        <v>0.928708489289081</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.982014529064315</v>
+        <v>6.798277304615253</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07341199664760054</v>
+        <v>0.07327964306570109</v>
       </c>
       <c r="C40">
-        <v>2046.881241016054</v>
+        <v>2014.71499279071</v>
       </c>
       <c r="D40">
-        <v>3266.019241016054</v>
+        <v>3267.20399279071</v>
       </c>
       <c r="E40">
-        <v>-1032.062</v>
+        <v>-998.711</v>
       </c>
       <c r="F40">
-        <v>1267.338</v>
+        <v>1300.689</v>
       </c>
       <c r="G40">
         <v>48.2</v>
@@ -4573,28 +4573,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M40">
-        <v>68.81645340000001</v>
+        <v>70.62741270000001</v>
       </c>
       <c r="N40">
-        <v>399.0168799333333</v>
+        <v>397.2059206333332</v>
       </c>
       <c r="O40">
-        <v>99.75421998333331</v>
+        <v>99.30148015833331</v>
       </c>
       <c r="P40">
-        <v>299.2626599499999</v>
+        <v>297.9044404749999</v>
       </c>
       <c r="Q40">
-        <v>780.2626599499999</v>
+        <v>778.9044404749999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09344596233483957</v>
+        <v>0.09409326732082146</v>
       </c>
       <c r="T40">
-        <v>0.928708489289081</v>
+        <v>0.9413256682940047</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.798277304615253</v>
+        <v>6.623962501932811</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07327964306570109</v>
+        <v>0.07314728948380164</v>
       </c>
       <c r="C41">
-        <v>2014.71499279071</v>
+        <v>1982.54960441708</v>
       </c>
       <c r="D41">
-        <v>3267.20399279071</v>
+        <v>3268.38960441708</v>
       </c>
       <c r="E41">
-        <v>-998.711</v>
+        <v>-965.3599999999999</v>
       </c>
       <c r="F41">
-        <v>1300.689</v>
+        <v>1334.04</v>
       </c>
       <c r="G41">
         <v>48.2</v>
@@ -4655,28 +4655,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M41">
-        <v>70.62741270000001</v>
+        <v>72.43837200000002</v>
       </c>
       <c r="N41">
-        <v>397.2059206333332</v>
+        <v>395.3949613333332</v>
       </c>
       <c r="O41">
-        <v>99.30148015833331</v>
+        <v>98.84874033333331</v>
       </c>
       <c r="P41">
-        <v>297.9044404749999</v>
+        <v>296.5462209999999</v>
       </c>
       <c r="Q41">
-        <v>778.9044404749999</v>
+        <v>777.5462209999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09409326732082146</v>
+        <v>0.0947621491396694</v>
       </c>
       <c r="T41">
-        <v>0.9413256682940047</v>
+        <v>0.9543634199324258</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.623962501932811</v>
+        <v>6.45836343938449</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07314728948380164</v>
+        <v>0.07301493590190219</v>
       </c>
       <c r="C42">
-        <v>1982.54960441708</v>
+        <v>1950.385076831581</v>
       </c>
       <c r="D42">
-        <v>3268.38960441708</v>
+        <v>3269.576076831582</v>
       </c>
       <c r="E42">
-        <v>-965.3599999999999</v>
+        <v>-932.0089999999998</v>
       </c>
       <c r="F42">
-        <v>1334.04</v>
+        <v>1367.391</v>
       </c>
       <c r="G42">
         <v>48.2</v>
@@ -4737,28 +4737,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M42">
-        <v>72.43837200000002</v>
+        <v>74.24933130000002</v>
       </c>
       <c r="N42">
-        <v>395.3949613333332</v>
+        <v>393.5840020333333</v>
       </c>
       <c r="O42">
-        <v>98.84874033333331</v>
+        <v>98.39600050833332</v>
       </c>
       <c r="P42">
-        <v>296.5462209999999</v>
+        <v>295.1880015249999</v>
       </c>
       <c r="Q42">
-        <v>777.5462209999999</v>
+        <v>776.1880015249999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0947621491396694</v>
+        <v>0.09545370491847829</v>
       </c>
       <c r="T42">
-        <v>0.9543634199324258</v>
+        <v>0.9678431292535054</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.45836343938449</v>
+        <v>6.300842379887308</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07301493590190219</v>
+        <v>0.07288258232000273</v>
       </c>
       <c r="C43">
-        <v>1950.385076831581</v>
+        <v>1918.221410971989</v>
       </c>
       <c r="D43">
-        <v>3269.576076831582</v>
+        <v>3270.76341097199</v>
       </c>
       <c r="E43">
-        <v>-932.0089999999998</v>
+        <v>-898.6579999999999</v>
       </c>
       <c r="F43">
-        <v>1367.391</v>
+        <v>1400.742</v>
       </c>
       <c r="G43">
         <v>48.2</v>
@@ -4819,28 +4819,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M43">
-        <v>74.24933130000002</v>
+        <v>76.06029060000002</v>
       </c>
       <c r="N43">
-        <v>393.5840020333333</v>
+        <v>391.7730427333332</v>
       </c>
       <c r="O43">
-        <v>98.39600050833332</v>
+        <v>97.94326068333331</v>
       </c>
       <c r="P43">
-        <v>295.1880015249999</v>
+        <v>293.8297820499999</v>
       </c>
       <c r="Q43">
-        <v>776.1880015249999</v>
+        <v>774.8297820499999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09545370491847829</v>
+        <v>0.09616910744828058</v>
       </c>
       <c r="T43">
-        <v>0.9678431292535054</v>
+        <v>0.9817876561373806</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.300842379887308</v>
+        <v>6.150822323223324</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07288258232000275</v>
+        <v>0.07307272873810329</v>
       </c>
       <c r="C44">
-        <v>1918.221410971989</v>
+        <v>1883.164891941158</v>
       </c>
       <c r="D44">
-        <v>3270.76341097199</v>
+        <v>3269.057891941159</v>
       </c>
       <c r="E44">
-        <v>-898.6579999999999</v>
+        <v>-865.307</v>
       </c>
       <c r="F44">
-        <v>1400.742</v>
+        <v>1434.093</v>
       </c>
       <c r="G44">
         <v>48.2</v>
@@ -4901,45 +4901,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M44">
-        <v>76.06029060000002</v>
+        <v>79.30534290000001</v>
       </c>
       <c r="N44">
-        <v>391.7730427333332</v>
+        <v>388.5279904333332</v>
       </c>
       <c r="O44">
-        <v>97.94326068333331</v>
+        <v>97.13199760833331</v>
       </c>
       <c r="P44">
-        <v>293.8297820499999</v>
+        <v>291.3959928249999</v>
       </c>
       <c r="Q44">
-        <v>774.8297820499999</v>
+        <v>772.3959928249999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09616910744828058</v>
+        <v>0.09690961182123384</v>
       </c>
       <c r="T44">
-        <v>0.9817876561373806</v>
+        <v>0.996221464666304</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.150822323223324</v>
+        <v>5.899140161631319</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07307272873810329</v>
+        <v>0.07294787515620385</v>
       </c>
       <c r="C45">
-        <v>1883.164891941158</v>
+        <v>1850.933566038663</v>
       </c>
       <c r="D45">
-        <v>3269.057891941159</v>
+        <v>3270.177566038663</v>
       </c>
       <c r="E45">
-        <v>-865.307</v>
+        <v>-831.9559999999999</v>
       </c>
       <c r="F45">
-        <v>1434.093</v>
+        <v>1467.444</v>
       </c>
       <c r="G45">
         <v>48.2</v>
@@ -4983,28 +4983,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M45">
-        <v>79.30534290000001</v>
+        <v>81.14965320000002</v>
       </c>
       <c r="N45">
-        <v>388.5279904333332</v>
+        <v>386.6836801333333</v>
       </c>
       <c r="O45">
-        <v>97.13199760833331</v>
+        <v>96.67092003333332</v>
       </c>
       <c r="P45">
-        <v>291.3959928249999</v>
+        <v>290.0127600999999</v>
       </c>
       <c r="Q45">
-        <v>772.3959928249999</v>
+        <v>771.0127600999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09690961182123384</v>
+        <v>0.09767656277893544</v>
       </c>
       <c r="T45">
-        <v>0.996221464666304</v>
+        <v>1.011170766356975</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.899140161631319</v>
+        <v>5.765068794321516</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07294787515620385</v>
+        <v>0.0728230215743044</v>
       </c>
       <c r="C46">
-        <v>1850.933566038663</v>
+        <v>1818.703007390627</v>
       </c>
       <c r="D46">
-        <v>3270.177566038663</v>
+        <v>3271.298007390627</v>
       </c>
       <c r="E46">
-        <v>-831.9559999999999</v>
+        <v>-798.6049999999998</v>
       </c>
       <c r="F46">
-        <v>1467.444</v>
+        <v>1500.795</v>
       </c>
       <c r="G46">
         <v>48.2</v>
@@ -5065,28 +5065,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M46">
-        <v>81.14965320000002</v>
+        <v>82.99396350000002</v>
       </c>
       <c r="N46">
-        <v>386.6836801333333</v>
+        <v>384.8393698333333</v>
       </c>
       <c r="O46">
-        <v>96.67092003333332</v>
+        <v>96.20984245833331</v>
       </c>
       <c r="P46">
-        <v>290.0127600999999</v>
+        <v>288.629527375</v>
       </c>
       <c r="Q46">
-        <v>771.0127600999999</v>
+        <v>769.629527375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09767656277893544</v>
+        <v>0.09847140286237162</v>
       </c>
       <c r="T46">
-        <v>1.011170766356975</v>
+        <v>1.026663679018216</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.765068794321516</v>
+        <v>5.636956154447705</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0728230215743044</v>
+        <v>0.07269816799240494</v>
       </c>
       <c r="C47">
-        <v>1818.703007390627</v>
+        <v>1786.47321678596</v>
       </c>
       <c r="D47">
-        <v>3271.298007390627</v>
+        <v>3272.41921678596</v>
       </c>
       <c r="E47">
-        <v>-798.6049999999998</v>
+        <v>-765.2539999999999</v>
       </c>
       <c r="F47">
-        <v>1500.795</v>
+        <v>1534.146</v>
       </c>
       <c r="G47">
         <v>48.2</v>
@@ -5147,28 +5147,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M47">
-        <v>82.99396350000002</v>
+        <v>84.83827380000001</v>
       </c>
       <c r="N47">
-        <v>384.8393698333333</v>
+        <v>382.9950595333332</v>
       </c>
       <c r="O47">
-        <v>96.20984245833331</v>
+        <v>95.74876488333331</v>
       </c>
       <c r="P47">
-        <v>288.629527375</v>
+        <v>287.2462946499999</v>
       </c>
       <c r="Q47">
-        <v>769.629527375</v>
+        <v>768.24629465</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09847140286237162</v>
+        <v>0.09929568146741655</v>
       </c>
       <c r="T47">
-        <v>1.026663679018216</v>
+        <v>1.042730403259502</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.636956154447705</v>
+        <v>5.514413629351016</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07269816799240494</v>
+        <v>0.07257331441050549</v>
       </c>
       <c r="C48">
-        <v>1786.47321678596</v>
+        <v>1754.244195014653</v>
       </c>
       <c r="D48">
-        <v>3272.41921678596</v>
+        <v>3273.541195014653</v>
       </c>
       <c r="E48">
-        <v>-765.2539999999999</v>
+        <v>-731.9029999999998</v>
       </c>
       <c r="F48">
-        <v>1534.146</v>
+        <v>1567.497</v>
       </c>
       <c r="G48">
         <v>48.2</v>
@@ -5229,28 +5229,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M48">
-        <v>84.83827380000001</v>
+        <v>86.68258410000001</v>
       </c>
       <c r="N48">
-        <v>382.9950595333332</v>
+        <v>381.1507492333333</v>
       </c>
       <c r="O48">
-        <v>95.74876488333331</v>
+        <v>95.28768730833332</v>
       </c>
       <c r="P48">
-        <v>287.2462946499999</v>
+        <v>285.863061925</v>
       </c>
       <c r="Q48">
-        <v>768.24629465</v>
+        <v>766.863061925</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09929568146741655</v>
+        <v>0.1001510649254821</v>
       </c>
       <c r="T48">
-        <v>1.042730403259502</v>
+        <v>1.059403418981592</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.514413629351016</v>
+        <v>5.397085679790356</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07257331441050549</v>
+        <v>0.07244846082860605</v>
       </c>
       <c r="C49">
-        <v>1754.244195014653</v>
+        <v>1722.015942867781</v>
       </c>
       <c r="D49">
-        <v>3273.541195014653</v>
+        <v>3274.663942867781</v>
       </c>
       <c r="E49">
-        <v>-731.9029999999998</v>
+        <v>-698.5519999999997</v>
       </c>
       <c r="F49">
-        <v>1567.497</v>
+        <v>1600.848</v>
       </c>
       <c r="G49">
         <v>48.2</v>
@@ -5311,28 +5311,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M49">
-        <v>86.68258410000001</v>
+        <v>88.52689440000003</v>
       </c>
       <c r="N49">
-        <v>381.1507492333333</v>
+        <v>379.3064389333332</v>
       </c>
       <c r="O49">
-        <v>95.28768730833332</v>
+        <v>94.8266097333333</v>
       </c>
       <c r="P49">
-        <v>285.863061925</v>
+        <v>284.4798291999999</v>
       </c>
       <c r="Q49">
-        <v>766.863061925</v>
+        <v>765.4798291999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1001510649254821</v>
+        <v>0.1010393477473193</v>
       </c>
       <c r="T49">
-        <v>1.059403418981592</v>
+        <v>1.076717704539147</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.397085679790356</v>
+        <v>5.284646394794722</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07244846082860605</v>
+        <v>0.07232360724670658</v>
       </c>
       <c r="C50">
-        <v>1722.015942867781</v>
+        <v>1689.788461137507</v>
       </c>
       <c r="D50">
-        <v>3274.663942867781</v>
+        <v>3275.787461137507</v>
       </c>
       <c r="E50">
-        <v>-698.5519999999999</v>
+        <v>-665.201</v>
       </c>
       <c r="F50">
-        <v>1600.848</v>
+        <v>1634.199</v>
       </c>
       <c r="G50">
         <v>48.2</v>
@@ -5393,28 +5393,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M50">
-        <v>88.52689440000002</v>
+        <v>90.37120470000001</v>
       </c>
       <c r="N50">
-        <v>379.3064389333333</v>
+        <v>377.4621286333332</v>
       </c>
       <c r="O50">
-        <v>94.82660973333331</v>
+        <v>94.36553215833331</v>
       </c>
       <c r="P50">
-        <v>284.4798291999999</v>
+        <v>283.096596475</v>
       </c>
       <c r="Q50">
-        <v>765.4798291999999</v>
+        <v>764.096596475</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1010393477473193</v>
+        <v>0.1019624651896208</v>
       </c>
       <c r="T50">
-        <v>1.076717704539147</v>
+        <v>1.094710981687194</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.284646394794724</v>
+        <v>5.176796468370341</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07232360724670658</v>
+        <v>0.07219875366480714</v>
       </c>
       <c r="C51">
-        <v>1689.788461137507</v>
+        <v>1657.561750617077</v>
       </c>
       <c r="D51">
-        <v>3275.787461137507</v>
+        <v>3276.911750617077</v>
       </c>
       <c r="E51">
-        <v>-665.201</v>
+        <v>-631.8499999999999</v>
       </c>
       <c r="F51">
-        <v>1634.199</v>
+        <v>1667.55</v>
       </c>
       <c r="G51">
         <v>48.2</v>
@@ -5475,28 +5475,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M51">
-        <v>90.37120470000001</v>
+        <v>92.21551500000001</v>
       </c>
       <c r="N51">
-        <v>377.4621286333332</v>
+        <v>375.6178183333333</v>
       </c>
       <c r="O51">
-        <v>94.36553215833331</v>
+        <v>93.90445458333332</v>
       </c>
       <c r="P51">
-        <v>283.096596475</v>
+        <v>281.71336375</v>
       </c>
       <c r="Q51">
-        <v>764.096596475</v>
+        <v>762.71336375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1019624651896208</v>
+        <v>0.1029225073296143</v>
       </c>
       <c r="T51">
-        <v>1.094710981687194</v>
+        <v>1.113423989921163</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.176796468370341</v>
+        <v>5.073260539002935</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07219875366480714</v>
+        <v>0.07207390008290769</v>
       </c>
       <c r="C52">
-        <v>1657.561750617077</v>
+        <v>1625.335812100831</v>
       </c>
       <c r="D52">
-        <v>3276.911750617077</v>
+        <v>3278.036812100832</v>
       </c>
       <c r="E52">
-        <v>-631.8499999999999</v>
+        <v>-598.4989999999998</v>
       </c>
       <c r="F52">
-        <v>1667.55</v>
+        <v>1700.901</v>
       </c>
       <c r="G52">
         <v>48.2</v>
@@ -5557,28 +5557,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M52">
-        <v>92.21551500000001</v>
+        <v>94.05982530000001</v>
       </c>
       <c r="N52">
-        <v>375.6178183333333</v>
+        <v>373.7735080333333</v>
       </c>
       <c r="O52">
-        <v>93.90445458333332</v>
+        <v>93.44337700833331</v>
       </c>
       <c r="P52">
-        <v>281.71336375</v>
+        <v>280.330131025</v>
       </c>
       <c r="Q52">
-        <v>762.71336375</v>
+        <v>761.3301310249999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1029225073296143</v>
+        <v>0.1039217348630769</v>
       </c>
       <c r="T52">
-        <v>1.113423989921163</v>
+        <v>1.13290079440958</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.073260539002935</v>
+        <v>4.973784842159739</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07207390008290769</v>
+        <v>0.07194904650100825</v>
       </c>
       <c r="C53">
-        <v>1625.335812100831</v>
+        <v>1593.110646384198</v>
       </c>
       <c r="D53">
-        <v>3278.036812100832</v>
+        <v>3279.162646384199</v>
       </c>
       <c r="E53">
-        <v>-598.4989999999998</v>
+        <v>-565.1479999999999</v>
       </c>
       <c r="F53">
-        <v>1700.901</v>
+        <v>1734.252</v>
       </c>
       <c r="G53">
         <v>48.2</v>
@@ -5639,28 +5639,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M53">
-        <v>94.05982530000001</v>
+        <v>95.90413560000002</v>
       </c>
       <c r="N53">
-        <v>373.7735080333333</v>
+        <v>371.9291977333332</v>
       </c>
       <c r="O53">
-        <v>93.44337700833331</v>
+        <v>92.98229943333331</v>
       </c>
       <c r="P53">
-        <v>280.330131025</v>
+        <v>278.9468982999999</v>
       </c>
       <c r="Q53">
-        <v>761.3301310249999</v>
+        <v>759.9468982999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1039217348630769</v>
+        <v>0.1049625968771005</v>
       </c>
       <c r="T53">
-        <v>1.13290079440958</v>
+        <v>1.153189132418348</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.973784842159739</v>
+        <v>4.878135133656667</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07194904650100825</v>
+        <v>0.0718241929191088</v>
       </c>
       <c r="C54">
-        <v>1593.110646384198</v>
+        <v>1560.8862542637</v>
       </c>
       <c r="D54">
-        <v>3279.162646384199</v>
+        <v>3280.289254263701</v>
       </c>
       <c r="E54">
-        <v>-565.1479999999999</v>
+        <v>-531.7969999999998</v>
       </c>
       <c r="F54">
-        <v>1734.252</v>
+        <v>1767.603</v>
       </c>
       <c r="G54">
         <v>48.2</v>
@@ -5721,28 +5721,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M54">
-        <v>95.90413560000002</v>
+        <v>97.74844590000002</v>
       </c>
       <c r="N54">
-        <v>371.9291977333332</v>
+        <v>370.0848874333332</v>
       </c>
       <c r="O54">
-        <v>92.98229943333331</v>
+        <v>92.52122185833331</v>
       </c>
       <c r="P54">
-        <v>278.9468982999999</v>
+        <v>277.5636655749999</v>
       </c>
       <c r="Q54">
-        <v>759.9468982999999</v>
+        <v>758.563665575</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1049625968771005</v>
+        <v>0.1060477508917209</v>
       </c>
       <c r="T54">
-        <v>1.153189132418348</v>
+        <v>1.174340803959403</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.878135133656667</v>
+        <v>4.786094848115976</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0718241929191088</v>
+        <v>0.07169933933720934</v>
       </c>
       <c r="C55">
-        <v>1560.8862542637</v>
+        <v>1528.662636536954</v>
       </c>
       <c r="D55">
-        <v>3280.289254263701</v>
+        <v>3281.416636536955</v>
       </c>
       <c r="E55">
-        <v>-531.7969999999998</v>
+        <v>-498.4459999999997</v>
       </c>
       <c r="F55">
-        <v>1767.603</v>
+        <v>1800.954</v>
       </c>
       <c r="G55">
         <v>48.2</v>
@@ -5803,28 +5803,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M55">
-        <v>97.74844590000002</v>
+        <v>99.59275620000003</v>
       </c>
       <c r="N55">
-        <v>370.0848874333332</v>
+        <v>368.2405771333332</v>
       </c>
       <c r="O55">
-        <v>92.52122185833331</v>
+        <v>92.0601442833333</v>
       </c>
       <c r="P55">
-        <v>277.5636655749999</v>
+        <v>276.1804328499999</v>
       </c>
       <c r="Q55">
-        <v>758.563665575</v>
+        <v>757.1804328499999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1060477508917209</v>
+        <v>0.1071800855156725</v>
       </c>
       <c r="T55">
-        <v>1.174340803959403</v>
+        <v>1.196412113393548</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.786094848115976</v>
+        <v>4.697463462039753</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07169933933720934</v>
+        <v>0.07157448575530991</v>
       </c>
       <c r="C56">
-        <v>1528.662636536954</v>
+        <v>1496.439794002675</v>
       </c>
       <c r="D56">
-        <v>3281.416636536955</v>
+        <v>3282.544794002676</v>
       </c>
       <c r="E56">
-        <v>-498.4459999999997</v>
+        <v>-465.0949999999998</v>
       </c>
       <c r="F56">
-        <v>1800.954</v>
+        <v>1834.305</v>
       </c>
       <c r="G56">
         <v>48.2</v>
@@ -5885,28 +5885,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M56">
-        <v>99.59275620000003</v>
+        <v>101.4370665</v>
       </c>
       <c r="N56">
-        <v>368.2405771333332</v>
+        <v>366.3962668333332</v>
       </c>
       <c r="O56">
-        <v>92.0601442833333</v>
+        <v>91.59906670833331</v>
       </c>
       <c r="P56">
-        <v>276.1804328499999</v>
+        <v>274.7972001249999</v>
       </c>
       <c r="Q56">
-        <v>757.1804328499999</v>
+        <v>755.7972001249999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1071800855156725</v>
+        <v>0.1083627461229109</v>
       </c>
       <c r="T56">
-        <v>1.196412113393548</v>
+        <v>1.219464369913655</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.697463462039753</v>
+        <v>4.612055035457213</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07157448575530991</v>
+        <v>0.07144963217341045</v>
       </c>
       <c r="C57">
-        <v>1496.439794002675</v>
+        <v>1464.217727460676</v>
       </c>
       <c r="D57">
-        <v>3282.544794002676</v>
+        <v>3283.673727460676</v>
       </c>
       <c r="E57">
-        <v>-465.0949999999998</v>
+        <v>-431.7439999999997</v>
       </c>
       <c r="F57">
-        <v>1834.305</v>
+        <v>1867.656</v>
       </c>
       <c r="G57">
         <v>48.2</v>
@@ -5967,28 +5967,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M57">
-        <v>101.4370665</v>
+        <v>103.2813768</v>
       </c>
       <c r="N57">
-        <v>366.3962668333332</v>
+        <v>364.5519565333332</v>
       </c>
       <c r="O57">
-        <v>91.59906670833331</v>
+        <v>91.13798913333331</v>
       </c>
       <c r="P57">
-        <v>274.7972001249999</v>
+        <v>273.4139673999999</v>
       </c>
       <c r="Q57">
-        <v>755.7972001249999</v>
+        <v>754.4139673999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1083627461229109</v>
+        <v>0.1095991640304783</v>
       </c>
       <c r="T57">
-        <v>1.219464369913655</v>
+        <v>1.243564456275585</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.612055035457213</v>
+        <v>4.529696909824048</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07144963217341045</v>
+        <v>0.07239352859151099</v>
       </c>
       <c r="C58">
-        <v>1464.217727460676</v>
+        <v>1422.351165899407</v>
       </c>
       <c r="D58">
-        <v>3283.673727460676</v>
+        <v>3275.158165899408</v>
       </c>
       <c r="E58">
-        <v>-431.7439999999997</v>
+        <v>-398.3929999999996</v>
       </c>
       <c r="F58">
-        <v>1867.656</v>
+        <v>1901.007000000001</v>
       </c>
       <c r="G58">
         <v>48.2</v>
@@ -6049,45 +6049,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M58">
-        <v>103.2813768</v>
+        <v>109.8782046</v>
       </c>
       <c r="N58">
-        <v>364.5519565333332</v>
+        <v>357.9551287333333</v>
       </c>
       <c r="O58">
-        <v>91.13798913333331</v>
+        <v>89.48878218333331</v>
       </c>
       <c r="P58">
-        <v>273.4139673999999</v>
+        <v>268.4663465499999</v>
       </c>
       <c r="Q58">
-        <v>754.4139673999999</v>
+        <v>749.4663465499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1095991640304783</v>
+        <v>0.1108930897477</v>
       </c>
       <c r="T58">
-        <v>1.243564456275585</v>
+        <v>1.268785476886907</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.529696909824048</v>
+        <v>4.257744609464917</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07239352859151099</v>
+        <v>0.07228742500961155</v>
       </c>
       <c r="C59">
-        <v>1422.351165899407</v>
+        <v>1389.95519785028</v>
       </c>
       <c r="D59">
-        <v>3275.158165899408</v>
+        <v>3276.113197850281</v>
       </c>
       <c r="E59">
-        <v>-398.3929999999996</v>
+        <v>-365.0419999999997</v>
       </c>
       <c r="F59">
-        <v>1901.007000000001</v>
+        <v>1934.358</v>
       </c>
       <c r="G59">
         <v>48.2</v>
@@ -6131,28 +6131,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M59">
-        <v>109.8782046</v>
+        <v>111.8058924</v>
       </c>
       <c r="N59">
-        <v>357.9551287333333</v>
+        <v>356.0274409333332</v>
       </c>
       <c r="O59">
-        <v>89.48878218333331</v>
+        <v>89.0068602333333</v>
       </c>
       <c r="P59">
-        <v>268.4663465499999</v>
+        <v>267.0205806999999</v>
       </c>
       <c r="Q59">
-        <v>749.4663465499999</v>
+        <v>748.0205806999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1108930897477</v>
+        <v>0.1122486309752656</v>
       </c>
       <c r="T59">
-        <v>1.268785476886907</v>
+        <v>1.295207498479721</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.257744609464917</v>
+        <v>4.184335219646555</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07228742500961155</v>
+        <v>0.07218132142771211</v>
       </c>
       <c r="C60">
-        <v>1389.95519785028</v>
+        <v>1357.559786935815</v>
       </c>
       <c r="D60">
-        <v>3276.113197850281</v>
+        <v>3277.068786935815</v>
       </c>
       <c r="E60">
-        <v>-365.0419999999999</v>
+        <v>-331.691</v>
       </c>
       <c r="F60">
-        <v>1934.358</v>
+        <v>1967.709</v>
       </c>
       <c r="G60">
         <v>48.2</v>
@@ -6213,28 +6213,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M60">
-        <v>111.8058924</v>
+        <v>113.7335802</v>
       </c>
       <c r="N60">
-        <v>356.0274409333333</v>
+        <v>354.0997531333333</v>
       </c>
       <c r="O60">
-        <v>89.00686023333331</v>
+        <v>88.52493828333331</v>
       </c>
       <c r="P60">
-        <v>267.0205806999999</v>
+        <v>265.5748148499999</v>
       </c>
       <c r="Q60">
-        <v>748.0205807</v>
+        <v>746.5748148499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1122486309752656</v>
+        <v>0.1136702961651515</v>
       </c>
       <c r="T60">
-        <v>1.295207498479721</v>
+        <v>1.322918399174623</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.184335219646556</v>
+        <v>4.113414283720344</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07218132142771211</v>
+        <v>0.07207521784581267</v>
       </c>
       <c r="C61">
-        <v>1357.559786935815</v>
+        <v>1325.164933643675</v>
       </c>
       <c r="D61">
-        <v>3277.068786935815</v>
+        <v>3278.024933643675</v>
       </c>
       <c r="E61">
-        <v>-331.691</v>
+        <v>-298.3399999999999</v>
       </c>
       <c r="F61">
-        <v>1967.709</v>
+        <v>2001.06</v>
       </c>
       <c r="G61">
         <v>48.2</v>
@@ -6295,28 +6295,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M61">
-        <v>113.7335802</v>
+        <v>115.661268</v>
       </c>
       <c r="N61">
-        <v>354.0997531333333</v>
+        <v>352.1720653333333</v>
       </c>
       <c r="O61">
-        <v>88.52493828333331</v>
+        <v>88.04301633333331</v>
       </c>
       <c r="P61">
-        <v>265.5748148499999</v>
+        <v>264.129049</v>
       </c>
       <c r="Q61">
-        <v>746.5748148499999</v>
+        <v>745.1290489999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1136702961651515</v>
+        <v>0.1151630446145316</v>
       </c>
       <c r="T61">
-        <v>1.322918399174623</v>
+        <v>1.35201484490427</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.113414283720344</v>
+        <v>4.04485737899167</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07207521784581267</v>
+        <v>0.07357036426391322</v>
       </c>
       <c r="C62">
-        <v>1325.164933643675</v>
+        <v>1278.391755492509</v>
       </c>
       <c r="D62">
-        <v>3278.024933643675</v>
+        <v>3264.60275549251</v>
       </c>
       <c r="E62">
-        <v>-298.3399999999999</v>
+        <v>-264.9889999999998</v>
       </c>
       <c r="F62">
-        <v>2001.06</v>
+        <v>2034.411</v>
       </c>
       <c r="G62">
         <v>48.2</v>
@@ -6377,45 +6377,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M62">
-        <v>115.661268</v>
+        <v>124.7093943</v>
       </c>
       <c r="N62">
-        <v>352.1720653333333</v>
+        <v>343.1239390333333</v>
       </c>
       <c r="O62">
-        <v>88.04301633333331</v>
+        <v>85.78098475833332</v>
       </c>
       <c r="P62">
-        <v>264.129049</v>
+        <v>257.342954275</v>
       </c>
       <c r="Q62">
-        <v>745.1290489999999</v>
+        <v>738.342954275</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1151630446145316</v>
+        <v>0.1167323442664441</v>
       </c>
       <c r="T62">
-        <v>1.35201484490427</v>
+        <v>1.38260341605595</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.04485737899167</v>
+        <v>3.751388064702783</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07357036426391322</v>
+        <v>0.07349051068201376</v>
       </c>
       <c r="C63">
-        <v>1278.391755492509</v>
+        <v>1245.754835296884</v>
       </c>
       <c r="D63">
-        <v>3264.60275549251</v>
+        <v>3265.316835296885</v>
       </c>
       <c r="E63">
-        <v>-264.9889999999998</v>
+        <v>-231.6379999999999</v>
       </c>
       <c r="F63">
-        <v>2034.411</v>
+        <v>2067.762</v>
       </c>
       <c r="G63">
         <v>48.2</v>
@@ -6459,28 +6459,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M63">
-        <v>124.7093943</v>
+        <v>126.7538106</v>
       </c>
       <c r="N63">
-        <v>343.1239390333333</v>
+        <v>341.0795227333332</v>
       </c>
       <c r="O63">
-        <v>85.78098475833332</v>
+        <v>85.26988068333331</v>
       </c>
       <c r="P63">
-        <v>257.342954275</v>
+        <v>255.8096420499999</v>
       </c>
       <c r="Q63">
-        <v>738.342954275</v>
+        <v>736.8096420499999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1167323442664441</v>
+        <v>0.1183842386368783</v>
       </c>
       <c r="T63">
-        <v>1.38260341605595</v>
+        <v>1.414801912005087</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.751388064702783</v>
+        <v>3.690881805594673</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07349051068201376</v>
+        <v>0.07341065710011431</v>
       </c>
       <c r="C64">
-        <v>1245.754835296884</v>
+        <v>1213.118227556748</v>
       </c>
       <c r="D64">
-        <v>3265.316835296885</v>
+        <v>3266.031227556748</v>
       </c>
       <c r="E64">
-        <v>-231.6379999999999</v>
+        <v>-198.2869999999998</v>
       </c>
       <c r="F64">
-        <v>2067.762</v>
+        <v>2101.113</v>
       </c>
       <c r="G64">
         <v>48.2</v>
@@ -6541,28 +6541,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M64">
-        <v>126.7538106</v>
+        <v>128.7982269</v>
       </c>
       <c r="N64">
-        <v>341.0795227333332</v>
+        <v>339.0351064333332</v>
       </c>
       <c r="O64">
-        <v>85.26988068333331</v>
+        <v>84.75877660833331</v>
       </c>
       <c r="P64">
-        <v>255.8096420499999</v>
+        <v>254.2763298249999</v>
       </c>
       <c r="Q64">
-        <v>736.8096420499999</v>
+        <v>735.2763298249999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1183842386368783</v>
+        <v>0.1201254245949036</v>
       </c>
       <c r="T64">
-        <v>1.414801912005087</v>
+        <v>1.448740867194719</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.690881805594673</v>
+        <v>3.632296380109043</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07341065710011431</v>
+        <v>0.07333080351821486</v>
       </c>
       <c r="C65">
-        <v>1213.118227556748</v>
+        <v>1180.481932477225</v>
       </c>
       <c r="D65">
-        <v>3266.031227556748</v>
+        <v>3266.745932477226</v>
       </c>
       <c r="E65">
-        <v>-198.2869999999998</v>
+        <v>-164.9359999999997</v>
       </c>
       <c r="F65">
-        <v>2101.113</v>
+        <v>2134.464</v>
       </c>
       <c r="G65">
         <v>48.2</v>
@@ -6623,28 +6623,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M65">
-        <v>128.7982269</v>
+        <v>130.8426432</v>
       </c>
       <c r="N65">
-        <v>339.0351064333332</v>
+        <v>336.9906901333333</v>
       </c>
       <c r="O65">
-        <v>84.75877660833331</v>
+        <v>84.24767253333331</v>
       </c>
       <c r="P65">
-        <v>254.2763298249999</v>
+        <v>252.7430175999999</v>
       </c>
       <c r="Q65">
-        <v>735.2763298249999</v>
+        <v>733.7430175999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1201254245949036</v>
+        <v>0.1219633431061524</v>
       </c>
       <c r="T65">
-        <v>1.448740867194719</v>
+        <v>1.484565319894885</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.632296380109043</v>
+        <v>3.575541749169839</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07333080351821486</v>
+        <v>0.07325094993631542</v>
       </c>
       <c r="C66">
-        <v>1180.481932477225</v>
+        <v>1147.845950263619</v>
       </c>
       <c r="D66">
-        <v>3266.745932477226</v>
+        <v>3267.46095026362</v>
       </c>
       <c r="E66">
-        <v>-164.9359999999997</v>
+        <v>-131.5849999999996</v>
       </c>
       <c r="F66">
-        <v>2134.464</v>
+        <v>2167.815000000001</v>
       </c>
       <c r="G66">
         <v>48.2</v>
@@ -6705,28 +6705,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M66">
-        <v>130.8426432</v>
+        <v>132.8870595</v>
       </c>
       <c r="N66">
-        <v>336.9906901333333</v>
+        <v>334.9462738333332</v>
       </c>
       <c r="O66">
-        <v>84.24767253333331</v>
+        <v>83.73656845833331</v>
       </c>
       <c r="P66">
-        <v>252.7430175999999</v>
+        <v>251.2097053749999</v>
       </c>
       <c r="Q66">
-        <v>733.7430175999999</v>
+        <v>732.2097053749999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1219633431061524</v>
+        <v>0.1239062855323298</v>
       </c>
       <c r="T66">
-        <v>1.484565319894885</v>
+        <v>1.522436884177918</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.575541749169839</v>
+        <v>3.520533414567226</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07325094993631542</v>
+        <v>0.07455709635441596</v>
       </c>
       <c r="C67">
-        <v>1147.845950263619</v>
+        <v>1102.838741964385</v>
       </c>
       <c r="D67">
-        <v>3267.46095026362</v>
+        <v>3255.804741964385</v>
       </c>
       <c r="E67">
-        <v>-131.5849999999996</v>
+        <v>-98.23399999999992</v>
       </c>
       <c r="F67">
-        <v>2167.815000000001</v>
+        <v>2201.166</v>
       </c>
       <c r="G67">
         <v>48.2</v>
@@ -6787,45 +6787,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M67">
-        <v>132.8870595</v>
+        <v>141.0947406</v>
       </c>
       <c r="N67">
-        <v>334.9462738333332</v>
+        <v>326.7385927333332</v>
       </c>
       <c r="O67">
-        <v>83.73656845833331</v>
+        <v>81.68464818333331</v>
       </c>
       <c r="P67">
-        <v>251.2097053749999</v>
+        <v>245.0539445499999</v>
       </c>
       <c r="Q67">
-        <v>732.2097053749999</v>
+        <v>726.0539445499999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1239062855323298</v>
+        <v>0.1259635186894587</v>
       </c>
       <c r="T67">
-        <v>1.522436884177918</v>
+        <v>1.562536187536423</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.520533414567226</v>
+        <v>3.315738994549973</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07455709635441596</v>
+        <v>0.07449824277251652</v>
       </c>
       <c r="C68">
-        <v>1102.838741964385</v>
+        <v>1070.011168933822</v>
       </c>
       <c r="D68">
-        <v>3255.804741964385</v>
+        <v>3256.328168933822</v>
       </c>
       <c r="E68">
-        <v>-98.23399999999992</v>
+        <v>-64.88299999999981</v>
       </c>
       <c r="F68">
-        <v>2201.166</v>
+        <v>2234.517</v>
       </c>
       <c r="G68">
         <v>48.2</v>
@@ -6869,28 +6869,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M68">
-        <v>141.0947406</v>
+        <v>143.2325397</v>
       </c>
       <c r="N68">
-        <v>326.7385927333332</v>
+        <v>324.6007936333332</v>
       </c>
       <c r="O68">
-        <v>81.68464818333331</v>
+        <v>81.15019840833331</v>
       </c>
       <c r="P68">
-        <v>245.0539445499999</v>
+        <v>243.4505952249999</v>
       </c>
       <c r="Q68">
-        <v>726.0539445499999</v>
+        <v>724.4505952249999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1259635186894587</v>
+        <v>0.1281454326439894</v>
       </c>
       <c r="T68">
-        <v>1.562536187536423</v>
+        <v>1.605065751704534</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.315738994549973</v>
+        <v>3.266250352840272</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07449824277251652</v>
+        <v>0.07443938919061707</v>
       </c>
       <c r="C69">
-        <v>1070.011168933822</v>
+        <v>1037.183764230213</v>
       </c>
       <c r="D69">
-        <v>3256.328168933822</v>
+        <v>3256.851764230213</v>
       </c>
       <c r="E69">
-        <v>-64.88299999999981</v>
+        <v>-31.5319999999997</v>
       </c>
       <c r="F69">
-        <v>2234.517</v>
+        <v>2267.868</v>
       </c>
       <c r="G69">
         <v>48.2</v>
@@ -6951,28 +6951,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M69">
-        <v>143.2325397</v>
+        <v>145.3703388</v>
       </c>
       <c r="N69">
-        <v>324.6007936333332</v>
+        <v>322.4629945333332</v>
       </c>
       <c r="O69">
-        <v>81.15019840833331</v>
+        <v>80.61574863333331</v>
       </c>
       <c r="P69">
-        <v>243.4505952249999</v>
+        <v>241.8472458999999</v>
       </c>
       <c r="Q69">
-        <v>724.4505952249999</v>
+        <v>722.8472459</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1281454326439894</v>
+        <v>0.1304637162206783</v>
       </c>
       <c r="T69">
-        <v>1.605065751704534</v>
+        <v>1.650253413633153</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.266250352840272</v>
+        <v>3.21821725941615</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07443938919061707</v>
+        <v>0.07438053560871762</v>
       </c>
       <c r="C70">
-        <v>1037.183764230213</v>
+        <v>1004.356527934767</v>
       </c>
       <c r="D70">
-        <v>3256.851764230213</v>
+        <v>3257.375527934768</v>
       </c>
       <c r="E70">
-        <v>-31.5319999999997</v>
+        <v>1.819000000000415</v>
       </c>
       <c r="F70">
-        <v>2267.868</v>
+        <v>2301.219000000001</v>
       </c>
       <c r="G70">
         <v>48.2</v>
@@ -7033,28 +7033,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M70">
-        <v>145.3703388</v>
+        <v>147.5081379</v>
       </c>
       <c r="N70">
-        <v>322.4629945333332</v>
+        <v>320.3251954333332</v>
       </c>
       <c r="O70">
-        <v>80.61574863333331</v>
+        <v>80.0812988583333</v>
       </c>
       <c r="P70">
-        <v>241.8472458999999</v>
+        <v>240.2438965749999</v>
       </c>
       <c r="Q70">
-        <v>722.8472459</v>
+        <v>721.2438965749999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1304637162206783</v>
+        <v>0.1329315664797343</v>
       </c>
       <c r="T70">
-        <v>1.650253413633153</v>
+        <v>1.698356408589425</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.21821725941615</v>
+        <v>3.171576429569539</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07438053560871762</v>
+        <v>0.07432168202681817</v>
       </c>
       <c r="C71">
-        <v>1004.356527934767</v>
+        <v>971.5294601287474</v>
       </c>
       <c r="D71">
-        <v>3257.375527934768</v>
+        <v>3257.899460128748</v>
       </c>
       <c r="E71">
-        <v>1.819000000000415</v>
+        <v>35.17000000000053</v>
       </c>
       <c r="F71">
-        <v>2301.219000000001</v>
+        <v>2334.570000000001</v>
       </c>
       <c r="G71">
         <v>48.2</v>
@@ -7115,28 +7115,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M71">
-        <v>147.5081379</v>
+        <v>149.6459370000001</v>
       </c>
       <c r="N71">
-        <v>320.3251954333332</v>
+        <v>318.1873963333332</v>
       </c>
       <c r="O71">
-        <v>80.0812988583333</v>
+        <v>79.5468490833333</v>
       </c>
       <c r="P71">
-        <v>240.2438965749999</v>
+        <v>238.6405472499999</v>
       </c>
       <c r="Q71">
-        <v>721.2438965749999</v>
+        <v>719.6405472499998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1329315664797343</v>
+        <v>0.1355639400893939</v>
       </c>
       <c r="T71">
-        <v>1.698356408589425</v>
+        <v>1.749666269876114</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.171576429569539</v>
+        <v>3.126268194861402</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07432168202681817</v>
+        <v>0.07426282844491873</v>
       </c>
       <c r="C72">
-        <v>971.5294601287474</v>
+        <v>938.7025608934687</v>
       </c>
       <c r="D72">
-        <v>3257.899460128748</v>
+        <v>3258.42356089347</v>
       </c>
       <c r="E72">
-        <v>35.17000000000053</v>
+        <v>68.52100000000064</v>
       </c>
       <c r="F72">
-        <v>2334.570000000001</v>
+        <v>2367.921000000001</v>
       </c>
       <c r="G72">
         <v>48.2</v>
@@ -7197,28 +7197,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M72">
-        <v>149.6459370000001</v>
+        <v>151.7837361000001</v>
       </c>
       <c r="N72">
-        <v>318.1873963333332</v>
+        <v>316.0495972333332</v>
       </c>
       <c r="O72">
-        <v>79.5468490833333</v>
+        <v>79.0123993083333</v>
       </c>
       <c r="P72">
-        <v>238.6405472499999</v>
+        <v>237.0371979249999</v>
       </c>
       <c r="Q72">
-        <v>719.6405472499998</v>
+        <v>718.0371979249999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1355639400893939</v>
+        <v>0.1383778567066163</v>
       </c>
       <c r="T72">
-        <v>1.749666269876114</v>
+        <v>1.804514742286024</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.126268194861402</v>
+        <v>3.082236248454903</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07426282844491872</v>
+        <v>0.07420397486301927</v>
       </c>
       <c r="C73">
-        <v>938.7025608934691</v>
+        <v>905.8758303102995</v>
       </c>
       <c r="D73">
-        <v>3258.42356089347</v>
+        <v>3258.9478303103</v>
       </c>
       <c r="E73">
-        <v>68.52100000000019</v>
+        <v>101.8720000000003</v>
       </c>
       <c r="F73">
-        <v>2367.921</v>
+        <v>2401.272</v>
       </c>
       <c r="G73">
         <v>48.2</v>
@@ -7279,28 +7279,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M73">
-        <v>151.7837361</v>
+        <v>153.9215352</v>
       </c>
       <c r="N73">
-        <v>316.0495972333332</v>
+        <v>313.9117981333333</v>
       </c>
       <c r="O73">
-        <v>79.0123993083333</v>
+        <v>78.47794953333332</v>
       </c>
       <c r="P73">
-        <v>237.0371979249999</v>
+        <v>235.4338485999999</v>
       </c>
       <c r="Q73">
-        <v>718.0371979249999</v>
+        <v>716.4338485999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1383778567066163</v>
+        <v>0.1413927673679259</v>
       </c>
       <c r="T73">
-        <v>1.804514742286023</v>
+        <v>1.863280962725212</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.082236248454904</v>
+        <v>3.039427411670808</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07420397486301927</v>
+        <v>0.07841562128111981</v>
       </c>
       <c r="C74">
-        <v>905.8758303102995</v>
+        <v>835.4284527259815</v>
       </c>
       <c r="D74">
-        <v>3258.9478303103</v>
+        <v>3221.851452725982</v>
       </c>
       <c r="E74">
-        <v>101.8720000000003</v>
+        <v>135.223</v>
       </c>
       <c r="F74">
-        <v>2401.272</v>
+        <v>2434.623</v>
       </c>
       <c r="G74">
         <v>48.2</v>
@@ -7361,45 +7361,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M74">
-        <v>153.9215352</v>
+        <v>175.0493937</v>
       </c>
       <c r="N74">
-        <v>313.9117981333333</v>
+        <v>292.7839396333333</v>
       </c>
       <c r="O74">
-        <v>78.47794953333332</v>
+        <v>73.19598490833332</v>
       </c>
       <c r="P74">
-        <v>235.4338485999999</v>
+        <v>219.5879547249999</v>
       </c>
       <c r="Q74">
-        <v>716.4338485999999</v>
+        <v>700.5879547249999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1413927673679259</v>
+        <v>0.1446310047448882</v>
       </c>
       <c r="T74">
-        <v>1.863280962725212</v>
+        <v>1.926400236530267</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.039427411670808</v>
+        <v>2.672578998674551</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07841562128111981</v>
+        <v>0.07841526769922037</v>
       </c>
       <c r="C75">
-        <v>835.4284527259815</v>
+        <v>802.0805316441329</v>
       </c>
       <c r="D75">
-        <v>3221.851452725982</v>
+        <v>3221.854531644133</v>
       </c>
       <c r="E75">
-        <v>135.223</v>
+        <v>168.5740000000001</v>
       </c>
       <c r="F75">
-        <v>2434.623</v>
+        <v>2467.974</v>
       </c>
       <c r="G75">
         <v>48.2</v>
@@ -7443,28 +7443,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M75">
-        <v>175.0493937</v>
+        <v>177.4473306</v>
       </c>
       <c r="N75">
-        <v>292.7839396333333</v>
+        <v>290.3860027333333</v>
       </c>
       <c r="O75">
-        <v>73.19598490833332</v>
+        <v>72.59650068333332</v>
       </c>
       <c r="P75">
-        <v>219.5879547249999</v>
+        <v>217.78950205</v>
       </c>
       <c r="Q75">
-        <v>700.5879547249999</v>
+        <v>698.78950205</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1446310047448882</v>
+        <v>0.1481183373046937</v>
       </c>
       <c r="T75">
-        <v>1.926400236530267</v>
+        <v>1.994374839089556</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.672578998674551</v>
+        <v>2.63646306626003</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07841526769922037</v>
+        <v>0.07841491411732093</v>
       </c>
       <c r="C76">
-        <v>802.0805316441329</v>
+        <v>768.7326105681686</v>
       </c>
       <c r="D76">
-        <v>3221.854531644133</v>
+        <v>3221.857610568169</v>
       </c>
       <c r="E76">
-        <v>168.5740000000001</v>
+        <v>201.9250000000002</v>
       </c>
       <c r="F76">
-        <v>2467.974</v>
+        <v>2501.325</v>
       </c>
       <c r="G76">
         <v>48.2</v>
@@ -7525,28 +7525,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M76">
-        <v>177.4473306</v>
+        <v>179.8452675</v>
       </c>
       <c r="N76">
-        <v>290.3860027333333</v>
+        <v>287.9880658333332</v>
       </c>
       <c r="O76">
-        <v>72.59650068333332</v>
+        <v>71.99701645833331</v>
       </c>
       <c r="P76">
-        <v>217.78950205</v>
+        <v>215.9910493749999</v>
       </c>
       <c r="Q76">
-        <v>698.78950205</v>
+        <v>696.9910493749999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1481183373046937</v>
+        <v>0.1518846564692837</v>
       </c>
       <c r="T76">
-        <v>1.994374839089556</v>
+        <v>2.067787409853589</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.63646306626003</v>
+        <v>2.601310225376563</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07841491411732093</v>
+        <v>0.07841456053542148</v>
       </c>
       <c r="C77">
-        <v>768.7326105681686</v>
+        <v>735.3846894980893</v>
       </c>
       <c r="D77">
-        <v>3221.857610568169</v>
+        <v>3221.86068949809</v>
       </c>
       <c r="E77">
-        <v>201.9250000000002</v>
+        <v>235.2760000000003</v>
       </c>
       <c r="F77">
-        <v>2501.325</v>
+        <v>2534.676</v>
       </c>
       <c r="G77">
         <v>48.2</v>
@@ -7607,28 +7607,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M77">
-        <v>179.8452675</v>
+        <v>182.2432044000001</v>
       </c>
       <c r="N77">
-        <v>287.9880658333332</v>
+        <v>285.5901289333332</v>
       </c>
       <c r="O77">
-        <v>71.99701645833331</v>
+        <v>71.39753223333329</v>
       </c>
       <c r="P77">
-        <v>215.9910493749999</v>
+        <v>214.1925966999999</v>
       </c>
       <c r="Q77">
-        <v>696.9910493749999</v>
+        <v>695.1925966999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1518846564692837</v>
+        <v>0.1559648355642561</v>
       </c>
       <c r="T77">
-        <v>2.067787409853589</v>
+        <v>2.147317694847958</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.601310225376563</v>
+        <v>2.567082459253186</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07841456053542148</v>
+        <v>0.07841420695352203</v>
       </c>
       <c r="C78">
-        <v>735.3846894980893</v>
+        <v>702.0367684338948</v>
       </c>
       <c r="D78">
-        <v>3221.86068949809</v>
+        <v>3221.863768433896</v>
       </c>
       <c r="E78">
-        <v>235.2760000000003</v>
+        <v>268.6270000000004</v>
       </c>
       <c r="F78">
-        <v>2534.676</v>
+        <v>2568.027</v>
       </c>
       <c r="G78">
         <v>48.2</v>
@@ -7689,28 +7689,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M78">
-        <v>182.2432044000001</v>
+        <v>184.6411413</v>
       </c>
       <c r="N78">
-        <v>285.5901289333332</v>
+        <v>283.1921920333332</v>
       </c>
       <c r="O78">
-        <v>71.39753223333329</v>
+        <v>70.7980480083333</v>
       </c>
       <c r="P78">
-        <v>214.1925966999999</v>
+        <v>212.3941440249999</v>
       </c>
       <c r="Q78">
-        <v>695.1925966999999</v>
+        <v>693.3941440249998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1559648355642561</v>
+        <v>0.1603998128414001</v>
       </c>
       <c r="T78">
-        <v>2.147317694847958</v>
+        <v>2.233763656798359</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.567082459253186</v>
+        <v>2.533743726016132</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07841420695352203</v>
+        <v>0.07841385337162257</v>
       </c>
       <c r="C79">
-        <v>702.0367684338948</v>
+        <v>668.6888473755853</v>
       </c>
       <c r="D79">
-        <v>3221.863768433896</v>
+        <v>3221.866847375586</v>
       </c>
       <c r="E79">
-        <v>268.6270000000004</v>
+        <v>301.9780000000001</v>
       </c>
       <c r="F79">
-        <v>2568.027</v>
+        <v>2601.378</v>
       </c>
       <c r="G79">
         <v>48.2</v>
@@ -7771,28 +7771,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M79">
-        <v>184.6411413</v>
+        <v>187.0390782</v>
       </c>
       <c r="N79">
-        <v>283.1921920333332</v>
+        <v>280.7942551333332</v>
       </c>
       <c r="O79">
-        <v>70.7980480083333</v>
+        <v>70.1985637833333</v>
       </c>
       <c r="P79">
-        <v>212.3941440249999</v>
+        <v>210.5956913499999</v>
       </c>
       <c r="Q79">
-        <v>693.3941440249998</v>
+        <v>691.5956913499999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1603998128414001</v>
+        <v>0.1652379698710117</v>
       </c>
       <c r="T79">
-        <v>2.233763656798359</v>
+        <v>2.328068342562433</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.533743726016132</v>
+        <v>2.501259832092848</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07841385337162257</v>
+        <v>0.08072424978972313</v>
       </c>
       <c r="C80">
-        <v>668.6888473755853</v>
+        <v>615.3440686901799</v>
       </c>
       <c r="D80">
-        <v>3221.866847375586</v>
+        <v>3201.87306869018</v>
       </c>
       <c r="E80">
-        <v>301.9780000000001</v>
+        <v>335.3290000000002</v>
       </c>
       <c r="F80">
-        <v>2601.378</v>
+        <v>2634.729</v>
       </c>
       <c r="G80">
         <v>48.2</v>
@@ -7853,45 +7853,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M80">
-        <v>187.0390782</v>
+        <v>199.7124582</v>
       </c>
       <c r="N80">
-        <v>280.7942551333332</v>
+        <v>268.1208751333332</v>
       </c>
       <c r="O80">
-        <v>70.1985637833333</v>
+        <v>67.03021878333331</v>
       </c>
       <c r="P80">
-        <v>210.5956913499999</v>
+        <v>201.0906563499999</v>
       </c>
       <c r="Q80">
-        <v>691.5956913499999</v>
+        <v>682.0906563499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1652379698710117</v>
+        <v>0.1705369037605863</v>
       </c>
       <c r="T80">
-        <v>2.328068342562433</v>
+        <v>2.431354426970704</v>
       </c>
       <c r="U80">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.501259832092848</v>
+        <v>2.34253454967154</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08072424978972313</v>
+        <v>0.08075314620782369</v>
       </c>
       <c r="C81">
-        <v>615.3440686901799</v>
+        <v>581.7445750905449</v>
       </c>
       <c r="D81">
-        <v>3201.87306869018</v>
+        <v>3201.624575090545</v>
       </c>
       <c r="E81">
-        <v>335.3290000000002</v>
+        <v>368.6800000000003</v>
       </c>
       <c r="F81">
-        <v>2634.729</v>
+        <v>2668.08</v>
       </c>
       <c r="G81">
         <v>48.2</v>
@@ -7935,28 +7935,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M81">
-        <v>199.7124582</v>
+        <v>202.2404640000001</v>
       </c>
       <c r="N81">
-        <v>268.1208751333332</v>
+        <v>265.5928693333332</v>
       </c>
       <c r="O81">
-        <v>67.03021878333331</v>
+        <v>66.39821733333329</v>
       </c>
       <c r="P81">
-        <v>201.0906563499999</v>
+        <v>199.1946519999999</v>
       </c>
       <c r="Q81">
-        <v>682.0906563499999</v>
+        <v>680.1946519999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1705369037605863</v>
+        <v>0.1763657310391184</v>
       </c>
       <c r="T81">
-        <v>2.431354426970704</v>
+        <v>2.544969119819803</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.34253454967154</v>
+        <v>2.313252867800645</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08075314620782369</v>
+        <v>0.08078204262592423</v>
       </c>
       <c r="C82">
-        <v>581.7445750905449</v>
+        <v>548.1451200585084</v>
       </c>
       <c r="D82">
-        <v>3201.624575090545</v>
+        <v>3201.376120058509</v>
       </c>
       <c r="E82">
-        <v>368.6800000000003</v>
+        <v>402.0310000000004</v>
       </c>
       <c r="F82">
-        <v>2668.08</v>
+        <v>2701.431</v>
       </c>
       <c r="G82">
         <v>48.2</v>
@@ -8017,28 +8017,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M82">
-        <v>202.2404640000001</v>
+        <v>204.7684698</v>
       </c>
       <c r="N82">
-        <v>265.5928693333332</v>
+        <v>263.0648635333332</v>
       </c>
       <c r="O82">
-        <v>66.39821733333329</v>
+        <v>65.7662158833333</v>
       </c>
       <c r="P82">
-        <v>199.1946519999999</v>
+        <v>197.2986476499999</v>
       </c>
       <c r="Q82">
-        <v>680.1946519999999</v>
+        <v>678.2986476499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1763657310391184</v>
+        <v>0.1828081190838118</v>
       </c>
       <c r="T82">
-        <v>2.544969119819803</v>
+        <v>2.670543254021438</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.313252867800645</v>
+        <v>2.284694190420391</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08078204262592423</v>
+        <v>0.08081093904402478</v>
       </c>
       <c r="C83">
-        <v>548.1451200585084</v>
+        <v>514.5457035850918</v>
       </c>
       <c r="D83">
-        <v>3201.376120058509</v>
+        <v>3201.127703585093</v>
       </c>
       <c r="E83">
-        <v>402.0310000000004</v>
+        <v>435.3820000000005</v>
       </c>
       <c r="F83">
-        <v>2701.431</v>
+        <v>2734.782000000001</v>
       </c>
       <c r="G83">
         <v>48.2</v>
@@ -8099,28 +8099,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M83">
-        <v>204.7684698</v>
+        <v>207.2964756000001</v>
       </c>
       <c r="N83">
-        <v>263.0648635333332</v>
+        <v>260.5368577333332</v>
       </c>
       <c r="O83">
-        <v>65.7662158833333</v>
+        <v>65.1342144333333</v>
       </c>
       <c r="P83">
-        <v>197.2986476499999</v>
+        <v>195.4026432999999</v>
       </c>
       <c r="Q83">
-        <v>678.2986476499999</v>
+        <v>676.4026432999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1828081190838118</v>
+        <v>0.1899663280223599</v>
       </c>
       <c r="T83">
-        <v>2.670543254021438</v>
+        <v>2.810070069801032</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.284694190420391</v>
+        <v>2.256832066146971</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08081093904402478</v>
+        <v>0.08083983546212534</v>
       </c>
       <c r="C84">
-        <v>514.5457035850918</v>
+        <v>480.9463256613203</v>
       </c>
       <c r="D84">
-        <v>3201.127703585093</v>
+        <v>3200.879325661321</v>
       </c>
       <c r="E84">
-        <v>435.3820000000005</v>
+        <v>468.7330000000006</v>
       </c>
       <c r="F84">
-        <v>2734.782000000001</v>
+        <v>2768.133000000001</v>
       </c>
       <c r="G84">
         <v>48.2</v>
@@ -8181,28 +8181,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M84">
-        <v>207.2964756000001</v>
+        <v>209.8244814000001</v>
       </c>
       <c r="N84">
-        <v>260.5368577333332</v>
+        <v>258.0088519333332</v>
       </c>
       <c r="O84">
-        <v>65.1342144333333</v>
+        <v>64.50221298333329</v>
       </c>
       <c r="P84">
-        <v>195.4026432999999</v>
+        <v>193.5066389499999</v>
       </c>
       <c r="Q84">
-        <v>676.4026432999999</v>
+        <v>674.5066389499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1899663280223599</v>
+        <v>0.1979666791889726</v>
       </c>
       <c r="T84">
-        <v>2.810070069801032</v>
+        <v>2.966011805084109</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.256832066146971</v>
+        <v>2.229641318362067</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08083983546212534</v>
+        <v>0.08086873188022589</v>
       </c>
       <c r="C85">
-        <v>480.9463256613203</v>
+        <v>447.3469862782213</v>
       </c>
       <c r="D85">
-        <v>3200.879325661321</v>
+        <v>3200.630986278222</v>
       </c>
       <c r="E85">
-        <v>468.7330000000006</v>
+        <v>502.0840000000003</v>
       </c>
       <c r="F85">
-        <v>2768.133000000001</v>
+        <v>2801.484</v>
       </c>
       <c r="G85">
         <v>48.2</v>
@@ -8263,28 +8263,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M85">
-        <v>209.8244814000001</v>
+        <v>212.3524872</v>
       </c>
       <c r="N85">
-        <v>258.0088519333332</v>
+        <v>255.4808461333332</v>
       </c>
       <c r="O85">
-        <v>64.50221298333329</v>
+        <v>63.8702115333333</v>
       </c>
       <c r="P85">
-        <v>193.5066389499999</v>
+        <v>191.6106345999999</v>
       </c>
       <c r="Q85">
-        <v>674.5066389499999</v>
+        <v>672.6106345999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1979666791889726</v>
+        <v>0.2069670742514119</v>
       </c>
       <c r="T85">
-        <v>2.966011805084109</v>
+        <v>3.14144625727757</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.229641318362067</v>
+        <v>2.203097969333948</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08086873188022589</v>
+        <v>0.08089762829832645</v>
       </c>
       <c r="C86">
-        <v>447.3469862782213</v>
+        <v>413.7476854268243</v>
       </c>
       <c r="D86">
-        <v>3200.630986278222</v>
+        <v>3200.382685426825</v>
       </c>
       <c r="E86">
-        <v>502.0840000000003</v>
+        <v>535.4349999999999</v>
       </c>
       <c r="F86">
-        <v>2801.484</v>
+        <v>2834.835</v>
       </c>
       <c r="G86">
         <v>48.2</v>
@@ -8345,28 +8345,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M86">
-        <v>212.3524872</v>
+        <v>214.880493</v>
       </c>
       <c r="N86">
-        <v>255.4808461333332</v>
+        <v>252.9528403333332</v>
       </c>
       <c r="O86">
-        <v>63.8702115333333</v>
+        <v>63.23821008333331</v>
       </c>
       <c r="P86">
-        <v>191.6106345999999</v>
+        <v>189.7146302499999</v>
       </c>
       <c r="Q86">
-        <v>672.6106345999999</v>
+        <v>670.7146302499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2069670742514118</v>
+        <v>0.2171675219888429</v>
       </c>
       <c r="T86">
-        <v>3.141446257277568</v>
+        <v>3.34027196976349</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.203097969333948</v>
+        <v>2.177179169694725</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08089762829832645</v>
+        <v>0.080926524716427</v>
       </c>
       <c r="C87">
-        <v>413.7476854268243</v>
+        <v>380.1484230981623</v>
       </c>
       <c r="D87">
-        <v>3200.382685426825</v>
+        <v>3200.134423098163</v>
       </c>
       <c r="E87">
-        <v>535.4349999999999</v>
+        <v>568.7860000000001</v>
       </c>
       <c r="F87">
-        <v>2834.835</v>
+        <v>2868.186</v>
       </c>
       <c r="G87">
         <v>48.2</v>
@@ -8427,28 +8427,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M87">
-        <v>214.880493</v>
+        <v>217.4084988</v>
       </c>
       <c r="N87">
-        <v>252.9528403333332</v>
+        <v>250.4248345333332</v>
       </c>
       <c r="O87">
-        <v>63.23821008333331</v>
+        <v>62.60620863333331</v>
       </c>
       <c r="P87">
-        <v>189.7146302499999</v>
+        <v>187.8186258999999</v>
       </c>
       <c r="Q87">
-        <v>670.7146302499999</v>
+        <v>668.8186258999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2171675219888429</v>
+        <v>0.228825176545907</v>
       </c>
       <c r="T87">
-        <v>3.34027196976349</v>
+        <v>3.567501355461687</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.177179169694725</v>
+        <v>2.15186313283781</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.080926524716427</v>
+        <v>0.08095542113452753</v>
       </c>
       <c r="C88">
-        <v>380.1484230981623</v>
+        <v>346.5491992832717</v>
       </c>
       <c r="D88">
-        <v>3200.134423098163</v>
+        <v>3199.886199283272</v>
       </c>
       <c r="E88">
-        <v>568.7860000000001</v>
+        <v>602.1370000000002</v>
       </c>
       <c r="F88">
-        <v>2868.186</v>
+        <v>2901.537</v>
       </c>
       <c r="G88">
         <v>48.2</v>
@@ -8509,28 +8509,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M88">
-        <v>217.4084988</v>
+        <v>219.9365046</v>
       </c>
       <c r="N88">
-        <v>250.4248345333332</v>
+        <v>247.8968287333332</v>
       </c>
       <c r="O88">
-        <v>62.60620863333331</v>
+        <v>61.97420718333331</v>
       </c>
       <c r="P88">
-        <v>187.8186258999999</v>
+        <v>185.9226215499999</v>
       </c>
       <c r="Q88">
-        <v>668.8186258999999</v>
+        <v>666.9226215499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.228825176545907</v>
+        <v>0.2422763164194425</v>
       </c>
       <c r="T88">
-        <v>3.567501355461687</v>
+        <v>3.829689108190375</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.15186313283781</v>
+        <v>2.127129073839674</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08095542113452753</v>
+        <v>0.08098431755262808</v>
       </c>
       <c r="C89">
-        <v>346.5491992832717</v>
+        <v>312.9500139731904</v>
       </c>
       <c r="D89">
-        <v>3199.886199283272</v>
+        <v>3199.638013973191</v>
       </c>
       <c r="E89">
-        <v>602.1370000000002</v>
+        <v>635.4880000000003</v>
       </c>
       <c r="F89">
-        <v>2901.537</v>
+        <v>2934.888</v>
       </c>
       <c r="G89">
         <v>48.2</v>
@@ -8591,28 +8591,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M89">
-        <v>219.9365046</v>
+        <v>222.4645104000001</v>
       </c>
       <c r="N89">
-        <v>247.8968287333332</v>
+        <v>245.3688229333332</v>
       </c>
       <c r="O89">
-        <v>61.97420718333331</v>
+        <v>61.3422057333333</v>
       </c>
       <c r="P89">
-        <v>185.9226215499999</v>
+        <v>184.0266171999999</v>
       </c>
       <c r="Q89">
-        <v>666.9226215499999</v>
+        <v>665.0266171999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2422763164194425</v>
+        <v>0.2579693129385674</v>
       </c>
       <c r="T89">
-        <v>3.829689108190375</v>
+        <v>4.135574819707179</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.127129073839674</v>
+        <v>2.102957152546041</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08098431755262808</v>
+        <v>0.08101321397072864</v>
       </c>
       <c r="C90">
-        <v>312.9500139731904</v>
+        <v>279.3508671589602</v>
       </c>
       <c r="D90">
-        <v>3199.638013973191</v>
+        <v>3199.389867158961</v>
       </c>
       <c r="E90">
-        <v>635.4880000000003</v>
+        <v>668.8390000000004</v>
       </c>
       <c r="F90">
-        <v>2934.888</v>
+        <v>2968.239</v>
       </c>
       <c r="G90">
         <v>48.2</v>
@@ -8673,28 +8673,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M90">
-        <v>222.4645104000001</v>
+        <v>224.9925162000001</v>
       </c>
       <c r="N90">
-        <v>245.3688229333332</v>
+        <v>242.8408171333332</v>
       </c>
       <c r="O90">
-        <v>61.3422057333333</v>
+        <v>60.7102042833333</v>
       </c>
       <c r="P90">
-        <v>184.0266171999999</v>
+        <v>182.1306128499999</v>
       </c>
       <c r="Q90">
-        <v>665.0266171999999</v>
+        <v>663.1306128499999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2579693129385674</v>
+        <v>0.2765155815520785</v>
       </c>
       <c r="T90">
-        <v>4.135574819707179</v>
+        <v>4.497076115136128</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.102957152546041</v>
+        <v>2.079328420494962</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08101321397072864</v>
+        <v>0.08104211038882919</v>
       </c>
       <c r="C91">
-        <v>279.3508671589602</v>
+        <v>245.751758831625</v>
       </c>
       <c r="D91">
-        <v>3199.389867158961</v>
+        <v>3199.141758831626</v>
       </c>
       <c r="E91">
-        <v>668.8390000000004</v>
+        <v>702.1900000000005</v>
       </c>
       <c r="F91">
-        <v>2968.239</v>
+        <v>3001.590000000001</v>
       </c>
       <c r="G91">
         <v>48.2</v>
@@ -8755,28 +8755,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M91">
-        <v>224.9925162000001</v>
+        <v>227.5205220000001</v>
       </c>
       <c r="N91">
-        <v>242.8408171333332</v>
+        <v>240.3128113333332</v>
       </c>
       <c r="O91">
-        <v>60.7102042833333</v>
+        <v>60.0782028333333</v>
       </c>
       <c r="P91">
-        <v>182.1306128499999</v>
+        <v>180.2346084999999</v>
       </c>
       <c r="Q91">
-        <v>663.1306128499999</v>
+        <v>661.2346084999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2765155815520785</v>
+        <v>0.2987711038882919</v>
       </c>
       <c r="T91">
-        <v>4.497076115136128</v>
+        <v>4.930877669650868</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.079328420494962</v>
+        <v>2.056224771378351</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08104211038882919</v>
+        <v>0.08107100680692975</v>
       </c>
       <c r="C92">
-        <v>245.751758831625</v>
+        <v>212.1526889822321</v>
       </c>
       <c r="D92">
-        <v>3199.141758831626</v>
+        <v>3198.893688982233</v>
       </c>
       <c r="E92">
-        <v>702.1900000000005</v>
+        <v>735.5410000000002</v>
       </c>
       <c r="F92">
-        <v>3001.590000000001</v>
+        <v>3034.941</v>
       </c>
       <c r="G92">
         <v>48.2</v>
@@ -8837,28 +8837,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M92">
-        <v>227.5205220000001</v>
+        <v>230.0485278</v>
       </c>
       <c r="N92">
-        <v>240.3128113333332</v>
+        <v>237.7848055333332</v>
       </c>
       <c r="O92">
-        <v>60.0782028333333</v>
+        <v>59.4462013833333</v>
       </c>
       <c r="P92">
-        <v>180.2346084999999</v>
+        <v>178.3386041499999</v>
       </c>
       <c r="Q92">
-        <v>661.2346084999999</v>
+        <v>659.3386041499999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2987711038882919</v>
+        <v>0.3259722978547749</v>
       </c>
       <c r="T92">
-        <v>4.930877669650868</v>
+        <v>5.461079569613327</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.056224771378351</v>
+        <v>2.033628894769798</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08107100680692975</v>
+        <v>0.0810999032250303</v>
       </c>
       <c r="C93">
-        <v>212.1526889822321</v>
+        <v>178.5536576018303</v>
       </c>
       <c r="D93">
-        <v>3198.893688982233</v>
+        <v>3198.645657601831</v>
       </c>
       <c r="E93">
-        <v>735.5410000000002</v>
+        <v>768.8920000000003</v>
       </c>
       <c r="F93">
-        <v>3034.941</v>
+        <v>3068.292</v>
       </c>
       <c r="G93">
         <v>48.2</v>
@@ -8919,28 +8919,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M93">
-        <v>230.0485278</v>
+        <v>232.5765336</v>
       </c>
       <c r="N93">
-        <v>237.7848055333332</v>
+        <v>235.2567997333332</v>
       </c>
       <c r="O93">
-        <v>59.4462013833333</v>
+        <v>58.81419993333331</v>
       </c>
       <c r="P93">
-        <v>178.3386041499999</v>
+        <v>176.4425997999999</v>
       </c>
       <c r="Q93">
-        <v>659.3386041499999</v>
+        <v>657.4425997999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3259722978547749</v>
+        <v>0.3599737903128788</v>
       </c>
       <c r="T93">
-        <v>5.461079569613327</v>
+        <v>6.123831944566402</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.033628894769798</v>
+        <v>2.011524232870126</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0810999032250303</v>
+        <v>0.09103329964313085</v>
       </c>
       <c r="C94">
-        <v>178.5536576018303</v>
+        <v>62.15972953556593</v>
       </c>
       <c r="D94">
-        <v>3198.645657601831</v>
+        <v>3115.602729535567</v>
       </c>
       <c r="E94">
-        <v>768.8920000000003</v>
+        <v>802.2430000000004</v>
       </c>
       <c r="F94">
-        <v>3068.292</v>
+        <v>3101.643</v>
       </c>
       <c r="G94">
         <v>48.2</v>
@@ -9001,45 +9001,45 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M94">
-        <v>232.5765336</v>
+        <v>279.14787</v>
       </c>
       <c r="N94">
-        <v>235.2567997333332</v>
+        <v>188.6854633333332</v>
       </c>
       <c r="O94">
-        <v>58.81419993333331</v>
+        <v>47.17136583333331</v>
       </c>
       <c r="P94">
-        <v>176.4425997999999</v>
+        <v>141.5140974999999</v>
       </c>
       <c r="Q94">
-        <v>657.4425997999999</v>
+        <v>622.5140974999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3599737903128788</v>
+        <v>0.4036899949018694</v>
       </c>
       <c r="T94">
-        <v>6.123831944566402</v>
+        <v>6.975942140934642</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.011524232870126</v>
+        <v>1.675933738392248</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09103329964313085</v>
+        <v>0.09116869606123139</v>
       </c>
       <c r="C95">
-        <v>62.15972953556593</v>
+        <v>27.7065956685633</v>
       </c>
       <c r="D95">
-        <v>3115.602729535567</v>
+        <v>3114.500595668564</v>
       </c>
       <c r="E95">
-        <v>802.2430000000004</v>
+        <v>835.5940000000005</v>
       </c>
       <c r="F95">
-        <v>3101.643</v>
+        <v>3134.994000000001</v>
       </c>
       <c r="G95">
         <v>48.2</v>
@@ -9083,28 +9083,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M95">
-        <v>279.14787</v>
+        <v>282.14946</v>
       </c>
       <c r="N95">
-        <v>188.6854633333332</v>
+        <v>185.6838733333332</v>
       </c>
       <c r="O95">
-        <v>47.17136583333331</v>
+        <v>46.42096833333331</v>
       </c>
       <c r="P95">
-        <v>141.5140974999999</v>
+        <v>139.2629049999999</v>
       </c>
       <c r="Q95">
-        <v>622.5140974999999</v>
+        <v>620.2629049999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4036899949018694</v>
+        <v>0.4619782676871902</v>
       </c>
       <c r="T95">
-        <v>6.975942140934642</v>
+        <v>8.112089069425625</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.675933738392248</v>
+        <v>1.658104656068926</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09116869606123139</v>
+        <v>0.09130409247933195</v>
       </c>
       <c r="C96">
-        <v>27.7065956685633</v>
+        <v>-6.745758721963739</v>
       </c>
       <c r="D96">
-        <v>3114.500595668564</v>
+        <v>3113.399241278037</v>
       </c>
       <c r="E96">
-        <v>835.5940000000005</v>
+        <v>868.9450000000006</v>
       </c>
       <c r="F96">
-        <v>3134.994000000001</v>
+        <v>3168.345000000001</v>
       </c>
       <c r="G96">
         <v>48.2</v>
@@ -9165,28 +9165,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M96">
-        <v>282.14946</v>
+        <v>285.1510500000001</v>
       </c>
       <c r="N96">
-        <v>185.6838733333332</v>
+        <v>182.6822833333332</v>
       </c>
       <c r="O96">
-        <v>46.42096833333331</v>
+        <v>45.6705708333333</v>
       </c>
       <c r="P96">
-        <v>139.2629049999999</v>
+        <v>137.0117124999999</v>
       </c>
       <c r="Q96">
-        <v>620.2629049999999</v>
+        <v>618.0117124999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4619782676871902</v>
+        <v>0.5435818495866395</v>
       </c>
       <c r="T96">
-        <v>8.112089069425625</v>
+        <v>9.702694769313009</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.658104656068926</v>
+        <v>1.640650922847148</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09130409247933195</v>
+        <v>0.0914394888974325</v>
       </c>
       <c r="C97">
-        <v>-6.745758721963739</v>
+        <v>-41.19733446264217</v>
       </c>
       <c r="D97">
-        <v>3113.399241278037</v>
+        <v>3112.298665537359</v>
       </c>
       <c r="E97">
-        <v>868.9450000000006</v>
+        <v>902.2960000000007</v>
       </c>
       <c r="F97">
-        <v>3168.345000000001</v>
+        <v>3201.696000000001</v>
       </c>
       <c r="G97">
         <v>48.2</v>
@@ -9247,28 +9247,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M97">
-        <v>285.1510500000001</v>
+        <v>288.1526400000001</v>
       </c>
       <c r="N97">
-        <v>182.6822833333332</v>
+        <v>179.6806933333332</v>
       </c>
       <c r="O97">
-        <v>45.6705708333333</v>
+        <v>44.9201733333333</v>
       </c>
       <c r="P97">
-        <v>137.0117124999999</v>
+        <v>134.7605199999999</v>
       </c>
       <c r="Q97">
-        <v>618.0117124999999</v>
+        <v>615.7605199999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5435818495866395</v>
+        <v>0.6659872224358134</v>
       </c>
       <c r="T97">
-        <v>9.702694769313009</v>
+        <v>12.08860331914408</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.640650922847148</v>
+        <v>1.62356080906749</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09143948889743249</v>
+        <v>0.09157488531553305</v>
       </c>
       <c r="C98">
-        <v>-41.19733446264127</v>
+        <v>-75.6481323789294</v>
       </c>
       <c r="D98">
-        <v>3112.298665537359</v>
+        <v>3111.198867621071</v>
       </c>
       <c r="E98">
-        <v>902.2960000000003</v>
+        <v>935.6470000000004</v>
       </c>
       <c r="F98">
-        <v>3201.696</v>
+        <v>3235.047</v>
       </c>
       <c r="G98">
         <v>48.2</v>
@@ -9329,28 +9329,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M98">
-        <v>288.15264</v>
+        <v>291.15423</v>
       </c>
       <c r="N98">
-        <v>179.6806933333332</v>
+        <v>176.6791033333332</v>
       </c>
       <c r="O98">
-        <v>44.92017333333331</v>
+        <v>44.1697758333333</v>
       </c>
       <c r="P98">
-        <v>134.7605199999999</v>
+        <v>132.5093274999999</v>
       </c>
       <c r="Q98">
-        <v>615.7605199999999</v>
+        <v>613.5093274999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6659872224358118</v>
+        <v>0.869996177184434</v>
       </c>
       <c r="T98">
-        <v>12.08860331914405</v>
+        <v>16.06511756886249</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.62356080906749</v>
+        <v>1.606823068767825</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09157488531553305</v>
+        <v>0.0917102817336336</v>
       </c>
       <c r="C99">
-        <v>-75.6481323789294</v>
+        <v>-110.0981532951182</v>
       </c>
       <c r="D99">
-        <v>3111.198867621071</v>
+        <v>3110.099846704882</v>
       </c>
       <c r="E99">
-        <v>935.6470000000004</v>
+        <v>968.998</v>
       </c>
       <c r="F99">
-        <v>3235.047</v>
+        <v>3268.398</v>
       </c>
       <c r="G99">
         <v>48.2</v>
@@ -9411,28 +9411,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M99">
-        <v>291.15423</v>
+        <v>294.15582</v>
       </c>
       <c r="N99">
-        <v>176.6791033333332</v>
+        <v>173.6775133333333</v>
       </c>
       <c r="O99">
-        <v>44.1697758333333</v>
+        <v>43.41937833333331</v>
       </c>
       <c r="P99">
-        <v>132.5093274999999</v>
+        <v>130.2581349999999</v>
       </c>
       <c r="Q99">
-        <v>613.5093274999999</v>
+        <v>611.2581349999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.869996177184434</v>
+        <v>1.278014086681679</v>
       </c>
       <c r="T99">
-        <v>16.06511756886249</v>
+        <v>24.01814606829937</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.606823068767825</v>
+        <v>1.590426915004888</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0917102817336336</v>
+        <v>0.09184567815173415</v>
       </c>
       <c r="C100">
-        <v>-110.0981532951182</v>
+        <v>-144.5473980343359</v>
       </c>
       <c r="D100">
-        <v>3110.099846704882</v>
+        <v>3109.001601965665</v>
       </c>
       <c r="E100">
-        <v>968.998</v>
+        <v>1002.349</v>
       </c>
       <c r="F100">
-        <v>3268.398</v>
+        <v>3301.749</v>
       </c>
       <c r="G100">
         <v>48.2</v>
@@ -9493,28 +9493,28 @@
         <v>467.8333333333333</v>
       </c>
       <c r="M100">
-        <v>294.15582</v>
+        <v>297.15741</v>
       </c>
       <c r="N100">
-        <v>173.6775133333333</v>
+        <v>170.6759233333332</v>
       </c>
       <c r="O100">
-        <v>43.41937833333331</v>
+        <v>42.66898083333331</v>
       </c>
       <c r="P100">
-        <v>130.2581349999999</v>
+        <v>128.0069424999999</v>
       </c>
       <c r="Q100">
-        <v>611.2581349999999</v>
+        <v>609.0069424999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.278014086681679</v>
+        <v>2.502067815173413</v>
       </c>
       <c r="T100">
-        <v>24.01814606829937</v>
+        <v>47.87723156660999</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.590426915004888</v>
+        <v>1.574361996671505</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09184567815173415</v>
-      </c>
-      <c r="C101">
-        <v>-144.5473980343359</v>
-      </c>
-      <c r="D101">
-        <v>3109.001601965665</v>
-      </c>
-      <c r="E101">
-        <v>1002.349</v>
-      </c>
-      <c r="F101">
-        <v>3301.749</v>
-      </c>
-      <c r="G101">
-        <v>48.2</v>
-      </c>
-      <c r="H101">
-        <v>1035.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>948.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>481</v>
-      </c>
-      <c r="L101">
-        <v>467.8333333333333</v>
-      </c>
-      <c r="M101">
-        <v>297.15741</v>
-      </c>
-      <c r="N101">
-        <v>170.6759233333332</v>
-      </c>
-      <c r="O101">
-        <v>42.66898083333331</v>
-      </c>
-      <c r="P101">
-        <v>128.0069424999999</v>
-      </c>
-      <c r="Q101">
-        <v>609.0069424999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.502067815173413</v>
-      </c>
-      <c r="T101">
-        <v>47.87723156660999</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.0675</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.574361996671505</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
